--- a/research/traditional_assets/database/data/kenya/kenya_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_green_renewable_energy.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1287036587116151</v>
+        <v>0.1283490477354802</v>
       </c>
       <c r="C2">
-        <v>1290.404563072733</v>
+        <v>1284.054469051006</v>
       </c>
       <c r="D2">
-        <v>1097.804563072733</v>
+        <v>1102.520469051007</v>
       </c>
       <c r="E2">
-        <v>-921.3</v>
+        <v>-910.2339999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.066</v>
       </c>
       <c r="G2">
         <v>192.6</v>
@@ -1451,28 +1451,28 @@
         <v>126.825</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5566197999999999</v>
       </c>
       <c r="N2">
-        <v>126.825</v>
+        <v>126.2683802</v>
       </c>
       <c r="O2">
-        <v>38.0475</v>
+        <v>37.88051406</v>
       </c>
       <c r="P2">
-        <v>88.7775</v>
+        <v>88.38786614</v>
       </c>
       <c r="Q2">
-        <v>210.5775</v>
+        <v>210.18786614</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1287036587116151</v>
+        <v>0.1292898461974548</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.5821281565246924</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>227.8485242530001</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1283490477354802</v>
+        <v>0.1279944367593454</v>
       </c>
       <c r="C3">
-        <v>1284.054469051006</v>
+        <v>1277.745066640251</v>
       </c>
       <c r="D3">
-        <v>1102.520469051007</v>
+        <v>1107.277066640251</v>
       </c>
       <c r="E3">
-        <v>-910.2339999999999</v>
+        <v>-899.168</v>
       </c>
       <c r="F3">
-        <v>11.066</v>
+        <v>22.132</v>
       </c>
       <c r="G3">
         <v>192.6</v>
@@ -1533,28 +1533,28 @@
         <v>126.825</v>
       </c>
       <c r="M3">
-        <v>0.5566197999999999</v>
+        <v>1.1132396</v>
       </c>
       <c r="N3">
-        <v>126.2683802</v>
+        <v>125.7117604</v>
       </c>
       <c r="O3">
-        <v>37.88051406</v>
+        <v>37.71352812</v>
       </c>
       <c r="P3">
-        <v>88.38786614</v>
+        <v>87.99823228</v>
       </c>
       <c r="Q3">
-        <v>210.18786614</v>
+        <v>209.79823228</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1292898461974548</v>
+        <v>0.1298879966932096</v>
       </c>
       <c r="T3">
-        <v>0.5821281565246924</v>
+        <v>0.5862987264954955</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>227.8485242530001</v>
+        <v>113.9242621265</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1279944367593454</v>
+        <v>0.1276398257832105</v>
       </c>
       <c r="C4">
-        <v>1277.745066640251</v>
+        <v>1271.476884789243</v>
       </c>
       <c r="D4">
-        <v>1107.277066640251</v>
+        <v>1112.074884789243</v>
       </c>
       <c r="E4">
-        <v>-899.168</v>
+        <v>-888.102</v>
       </c>
       <c r="F4">
-        <v>22.132</v>
+        <v>33.19799999999999</v>
       </c>
       <c r="G4">
         <v>192.6</v>
@@ -1615,28 +1615,28 @@
         <v>126.825</v>
       </c>
       <c r="M4">
-        <v>1.1132396</v>
+        <v>1.6698594</v>
       </c>
       <c r="N4">
-        <v>125.7117604</v>
+        <v>125.1551406</v>
       </c>
       <c r="O4">
-        <v>37.71352812</v>
+        <v>37.54654218</v>
       </c>
       <c r="P4">
-        <v>87.99823228</v>
+        <v>87.60859842000001</v>
       </c>
       <c r="Q4">
-        <v>209.79823228</v>
+        <v>209.40859842</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1298879966932096</v>
+        <v>0.1304984801888768</v>
       </c>
       <c r="T4">
-        <v>0.5862987264954955</v>
+        <v>0.5905552875997172</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.9242621265</v>
+        <v>75.94950808433336</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1276398257832105</v>
+        <v>0.1272852148070757</v>
       </c>
       <c r="C5">
-        <v>1271.476884789243</v>
+        <v>1265.250461654369</v>
       </c>
       <c r="D5">
-        <v>1112.074884789243</v>
+        <v>1116.914461654369</v>
       </c>
       <c r="E5">
-        <v>-888.102</v>
+        <v>-877.0359999999999</v>
       </c>
       <c r="F5">
-        <v>33.19799999999999</v>
+        <v>44.264</v>
       </c>
       <c r="G5">
         <v>192.6</v>
@@ -1697,28 +1697,28 @@
         <v>126.825</v>
       </c>
       <c r="M5">
-        <v>1.6698594</v>
+        <v>2.2264792</v>
       </c>
       <c r="N5">
-        <v>125.1551406</v>
+        <v>124.5985208</v>
       </c>
       <c r="O5">
-        <v>37.54654218</v>
+        <v>37.37955624</v>
       </c>
       <c r="P5">
-        <v>87.60859842000001</v>
+        <v>87.21896456</v>
       </c>
       <c r="Q5">
-        <v>209.40859842</v>
+        <v>209.01896456</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1304984801888768</v>
+        <v>0.1311216820907038</v>
       </c>
       <c r="T5">
-        <v>0.5905552875997172</v>
+        <v>0.5949005270602767</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.94950808433336</v>
+        <v>56.96213106325001</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1272852148070757</v>
+        <v>0.1269306038309408</v>
       </c>
       <c r="C6">
-        <v>1265.250461654369</v>
+        <v>1259.066344800854</v>
       </c>
       <c r="D6">
-        <v>1116.914461654369</v>
+        <v>1121.796344800854</v>
       </c>
       <c r="E6">
-        <v>-877.0359999999999</v>
+        <v>-865.9699999999999</v>
       </c>
       <c r="F6">
-        <v>44.264</v>
+        <v>55.33</v>
       </c>
       <c r="G6">
         <v>192.6</v>
@@ -1779,28 +1779,28 @@
         <v>126.825</v>
       </c>
       <c r="M6">
-        <v>2.2264792</v>
+        <v>2.783099</v>
       </c>
       <c r="N6">
-        <v>124.5985208</v>
+        <v>124.041901</v>
       </c>
       <c r="O6">
-        <v>37.37955624</v>
+        <v>37.2125703</v>
       </c>
       <c r="P6">
-        <v>87.21896456</v>
+        <v>86.8293307</v>
       </c>
       <c r="Q6">
-        <v>209.01896456</v>
+        <v>208.6293307</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1311216820907038</v>
+        <v>0.1317580040325693</v>
       </c>
       <c r="T6">
-        <v>0.5949005270602767</v>
+        <v>0.5993372452463219</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.96213106325001</v>
+        <v>45.5697048506</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1269306038309408</v>
+        <v>0.126575992854806</v>
       </c>
       <c r="C7">
-        <v>1259.066344800854</v>
+        <v>1252.925091409285</v>
       </c>
       <c r="D7">
-        <v>1121.796344800854</v>
+        <v>1126.721091409285</v>
       </c>
       <c r="E7">
-        <v>-865.9699999999999</v>
+        <v>-854.904</v>
       </c>
       <c r="F7">
-        <v>55.33</v>
+        <v>66.396</v>
       </c>
       <c r="G7">
         <v>192.6</v>
@@ -1861,28 +1861,28 @@
         <v>126.825</v>
       </c>
       <c r="M7">
-        <v>2.783099</v>
+        <v>3.3397188</v>
       </c>
       <c r="N7">
-        <v>124.041901</v>
+        <v>123.4852812</v>
       </c>
       <c r="O7">
-        <v>37.2125703</v>
+        <v>37.04558436</v>
       </c>
       <c r="P7">
-        <v>86.8293307</v>
+        <v>86.43969684000001</v>
       </c>
       <c r="Q7">
-        <v>208.6293307</v>
+        <v>208.23969684</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1317580040325693</v>
+        <v>0.1324078647391553</v>
       </c>
       <c r="T7">
-        <v>0.5993372452463219</v>
+        <v>0.6038683616916446</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.5697048506</v>
+        <v>37.97475404216667</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.126575992854806</v>
+        <v>0.1262213818786712</v>
       </c>
       <c r="C8">
-        <v>1252.925091409285</v>
+        <v>1246.827268487603</v>
       </c>
       <c r="D8">
-        <v>1126.721091409285</v>
+        <v>1131.689268487603</v>
       </c>
       <c r="E8">
-        <v>-854.904</v>
+        <v>-843.838</v>
       </c>
       <c r="F8">
-        <v>66.39599999999999</v>
+        <v>77.46199999999999</v>
       </c>
       <c r="G8">
         <v>192.6</v>
@@ -1943,28 +1943,28 @@
         <v>126.825</v>
       </c>
       <c r="M8">
-        <v>3.339718799999999</v>
+        <v>3.896338599999999</v>
       </c>
       <c r="N8">
-        <v>123.4852812</v>
+        <v>122.9286614</v>
       </c>
       <c r="O8">
-        <v>37.04558436</v>
+        <v>36.87859842</v>
       </c>
       <c r="P8">
-        <v>86.43969684000001</v>
+        <v>86.05006298000001</v>
       </c>
       <c r="Q8">
-        <v>208.23969684</v>
+        <v>207.85006298</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1324078647391553</v>
+        <v>0.1330717009448077</v>
       </c>
       <c r="T8">
-        <v>0.6038683616916446</v>
+        <v>0.6084969215013828</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.97475404216667</v>
+        <v>32.54978917900001</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1262213818786712</v>
+        <v>0.1258667709025363</v>
       </c>
       <c r="C9">
-        <v>1246.827268487603</v>
+        <v>1240.773453088731</v>
       </c>
       <c r="D9">
-        <v>1131.689268487603</v>
+        <v>1136.701453088731</v>
       </c>
       <c r="E9">
-        <v>-843.838</v>
+        <v>-832.7719999999999</v>
       </c>
       <c r="F9">
-        <v>77.462</v>
+        <v>88.52799999999999</v>
       </c>
       <c r="G9">
         <v>192.6</v>
@@ -2025,28 +2025,28 @@
         <v>126.825</v>
       </c>
       <c r="M9">
-        <v>3.8963386</v>
+        <v>4.452958399999999</v>
       </c>
       <c r="N9">
-        <v>122.9286614</v>
+        <v>122.3720416</v>
       </c>
       <c r="O9">
-        <v>36.87859842</v>
+        <v>36.71161248</v>
       </c>
       <c r="P9">
-        <v>86.05006298000001</v>
+        <v>85.66042912</v>
       </c>
       <c r="Q9">
-        <v>207.85006298</v>
+        <v>207.46042912</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1330717009448077</v>
+        <v>0.1337499683723221</v>
       </c>
       <c r="T9">
-        <v>0.6084969215013828</v>
+        <v>0.6132261021765502</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.549789179</v>
+        <v>28.481065531625</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1258667709025363</v>
+        <v>0.1255121599264015</v>
       </c>
       <c r="C10">
-        <v>1240.773453088731</v>
+        <v>1234.764232533998</v>
       </c>
       <c r="D10">
-        <v>1136.701453088731</v>
+        <v>1141.758232533998</v>
       </c>
       <c r="E10">
-        <v>-832.7719999999999</v>
+        <v>-821.7059999999999</v>
       </c>
       <c r="F10">
-        <v>88.52799999999999</v>
+        <v>99.59399999999999</v>
       </c>
       <c r="G10">
         <v>192.6</v>
@@ -2107,28 +2107,28 @@
         <v>126.825</v>
       </c>
       <c r="M10">
-        <v>4.452958399999999</v>
+        <v>5.009578199999999</v>
       </c>
       <c r="N10">
-        <v>122.3720416</v>
+        <v>121.8154218</v>
       </c>
       <c r="O10">
-        <v>36.71161248</v>
+        <v>36.54462654</v>
       </c>
       <c r="P10">
-        <v>85.66042912</v>
+        <v>85.27079526</v>
       </c>
       <c r="Q10">
-        <v>207.46042912</v>
+        <v>207.07079526</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1337499683723221</v>
+        <v>0.1344431427762653</v>
       </c>
       <c r="T10">
-        <v>0.6132261021765502</v>
+        <v>0.6180592208885343</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.481065531625</v>
+        <v>25.31650269477778</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1255121599264015</v>
+        <v>0.1251575489502666</v>
       </c>
       <c r="C11">
-        <v>1234.764232533998</v>
+        <v>1228.80020464257</v>
       </c>
       <c r="D11">
-        <v>1141.758232533998</v>
+        <v>1146.86020464257</v>
       </c>
       <c r="E11">
-        <v>-821.7059999999999</v>
+        <v>-810.64</v>
       </c>
       <c r="F11">
-        <v>99.59399999999999</v>
+        <v>110.66</v>
       </c>
       <c r="G11">
         <v>192.6</v>
@@ -2189,28 +2189,28 @@
         <v>126.825</v>
       </c>
       <c r="M11">
-        <v>5.009578199999999</v>
+        <v>5.566197999999999</v>
       </c>
       <c r="N11">
-        <v>121.8154218</v>
+        <v>121.258802</v>
       </c>
       <c r="O11">
-        <v>36.54462654</v>
+        <v>36.3776406</v>
       </c>
       <c r="P11">
-        <v>85.27079526</v>
+        <v>84.8811614</v>
       </c>
       <c r="Q11">
-        <v>207.07079526</v>
+        <v>206.6811614</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1344431427762653</v>
+        <v>0.1351517210558518</v>
       </c>
       <c r="T11">
-        <v>0.6180592208885343</v>
+        <v>0.6229997422385625</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.31650269477778</v>
+        <v>22.7848524253</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1251575489502666</v>
+        <v>0.1248029379741318</v>
       </c>
       <c r="C12">
-        <v>1228.80020464257</v>
+        <v>1222.881977967047</v>
       </c>
       <c r="D12">
-        <v>1146.86020464257</v>
+        <v>1152.007977967047</v>
       </c>
       <c r="E12">
-        <v>-810.64</v>
+        <v>-799.574</v>
       </c>
       <c r="F12">
-        <v>110.66</v>
+        <v>121.726</v>
       </c>
       <c r="G12">
         <v>192.6</v>
@@ -2271,28 +2271,28 @@
         <v>126.825</v>
       </c>
       <c r="M12">
-        <v>5.566198</v>
+        <v>6.122817799999999</v>
       </c>
       <c r="N12">
-        <v>121.258802</v>
+        <v>120.7021822</v>
       </c>
       <c r="O12">
-        <v>36.3776406</v>
+        <v>36.21065466</v>
       </c>
       <c r="P12">
-        <v>84.8811614</v>
+        <v>84.49152754000001</v>
       </c>
       <c r="Q12">
-        <v>206.6811614</v>
+        <v>206.29152754</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1351517210558518</v>
+        <v>0.1358762224428447</v>
       </c>
       <c r="T12">
-        <v>0.6229997422385625</v>
+        <v>0.6280512865402768</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.7848524253</v>
+        <v>20.71350220481818</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1248029379741318</v>
+        <v>0.1244483269979969</v>
       </c>
       <c r="C13">
-        <v>1222.881977967047</v>
+        <v>1217.01017203544</v>
       </c>
       <c r="D13">
-        <v>1152.007977967047</v>
+        <v>1157.20217203544</v>
       </c>
       <c r="E13">
-        <v>-799.574</v>
+        <v>-788.508</v>
       </c>
       <c r="F13">
-        <v>121.726</v>
+        <v>132.792</v>
       </c>
       <c r="G13">
         <v>192.6</v>
@@ -2353,28 +2353,28 @@
         <v>126.825</v>
       </c>
       <c r="M13">
-        <v>6.122817799999999</v>
+        <v>6.679437599999998</v>
       </c>
       <c r="N13">
-        <v>120.7021822</v>
+        <v>120.1455624</v>
       </c>
       <c r="O13">
-        <v>36.21065466</v>
+        <v>36.04366872</v>
       </c>
       <c r="P13">
-        <v>84.49152754000001</v>
+        <v>84.10189368</v>
       </c>
       <c r="Q13">
-        <v>206.29152754</v>
+        <v>205.90189368</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1358762224428447</v>
+        <v>0.1366171897704511</v>
       </c>
       <c r="T13">
-        <v>0.6280512865402768</v>
+        <v>0.6332176386670301</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.71350220481818</v>
+        <v>18.98737702108334</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1244483269979969</v>
+        <v>0.1240937160218621</v>
       </c>
       <c r="C14">
-        <v>1217.01017203544</v>
+        <v>1211.185417599723</v>
       </c>
       <c r="D14">
-        <v>1157.20217203544</v>
+        <v>1162.443417599723</v>
       </c>
       <c r="E14">
-        <v>-788.508</v>
+        <v>-777.442</v>
       </c>
       <c r="F14">
-        <v>132.792</v>
+        <v>143.858</v>
       </c>
       <c r="G14">
         <v>192.6</v>
@@ -2435,28 +2435,28 @@
         <v>126.825</v>
       </c>
       <c r="M14">
-        <v>6.679437599999998</v>
+        <v>7.2360574</v>
       </c>
       <c r="N14">
-        <v>120.1455624</v>
+        <v>119.5889426</v>
       </c>
       <c r="O14">
-        <v>36.04366872</v>
+        <v>35.87668278</v>
       </c>
       <c r="P14">
-        <v>84.10189368</v>
+        <v>83.71225982</v>
       </c>
       <c r="Q14">
-        <v>205.90189368</v>
+        <v>205.51225982</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1366171897704511</v>
+        <v>0.1373751908297265</v>
       </c>
       <c r="T14">
-        <v>0.6332176386670301</v>
+        <v>0.6385027575093408</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.98737702108334</v>
+        <v>17.52680955792308</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1240937160218621</v>
+        <v>0.1237391050457272</v>
       </c>
       <c r="C15">
-        <v>1211.185417599723</v>
+        <v>1205.40835689117</v>
       </c>
       <c r="D15">
-        <v>1162.443417599723</v>
+        <v>1167.73235689117</v>
       </c>
       <c r="E15">
-        <v>-777.442</v>
+        <v>-766.376</v>
       </c>
       <c r="F15">
-        <v>143.858</v>
+        <v>154.924</v>
       </c>
       <c r="G15">
         <v>192.6</v>
@@ -2517,28 +2517,28 @@
         <v>126.825</v>
       </c>
       <c r="M15">
-        <v>7.2360574</v>
+        <v>7.7926772</v>
       </c>
       <c r="N15">
-        <v>119.5889426</v>
+        <v>119.0323228</v>
       </c>
       <c r="O15">
-        <v>35.87668278</v>
+        <v>35.70969684</v>
       </c>
       <c r="P15">
-        <v>83.71225982</v>
+        <v>83.32262596000001</v>
       </c>
       <c r="Q15">
-        <v>205.51225982</v>
+        <v>205.12262596</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1373751908297265</v>
+        <v>0.1381508198206131</v>
       </c>
       <c r="T15">
-        <v>0.6385027575093408</v>
+        <v>0.6439107860921705</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.52680955792308</v>
+        <v>16.2748945895</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1237391050457272</v>
+        <v>0.1233844940695924</v>
       </c>
       <c r="C16">
-        <v>1205.40835689117</v>
+        <v>1199.679643882692</v>
       </c>
       <c r="D16">
-        <v>1167.73235689117</v>
+        <v>1173.069643882692</v>
       </c>
       <c r="E16">
-        <v>-766.376</v>
+        <v>-755.3099999999999</v>
       </c>
       <c r="F16">
-        <v>154.924</v>
+        <v>165.99</v>
       </c>
       <c r="G16">
         <v>192.6</v>
@@ -2599,28 +2599,28 @@
         <v>126.825</v>
       </c>
       <c r="M16">
-        <v>7.7926772</v>
+        <v>8.349297</v>
       </c>
       <c r="N16">
-        <v>119.0323228</v>
+        <v>118.475703</v>
       </c>
       <c r="O16">
-        <v>35.70969684</v>
+        <v>35.5427109</v>
       </c>
       <c r="P16">
-        <v>83.32262596000001</v>
+        <v>82.93299210000001</v>
       </c>
       <c r="Q16">
-        <v>205.12262596</v>
+        <v>204.7329921</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1381508198206131</v>
+        <v>0.1389446989054028</v>
       </c>
       <c r="T16">
-        <v>0.6439107860921705</v>
+        <v>0.6494460624063608</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.2748945895</v>
+        <v>15.18990161686667</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1233844940695924</v>
+        <v>0.1230298830934575</v>
       </c>
       <c r="C17">
-        <v>1199.679643882692</v>
+        <v>1193.999944558403</v>
       </c>
       <c r="D17">
-        <v>1173.069643882692</v>
+        <v>1178.455944558403</v>
       </c>
       <c r="E17">
-        <v>-755.3099999999999</v>
+        <v>-744.2439999999999</v>
       </c>
       <c r="F17">
-        <v>165.99</v>
+        <v>177.056</v>
       </c>
       <c r="G17">
         <v>192.6</v>
@@ -2681,28 +2681,28 @@
         <v>126.825</v>
       </c>
       <c r="M17">
-        <v>8.349296999999998</v>
+        <v>8.905916799999998</v>
       </c>
       <c r="N17">
-        <v>118.475703</v>
+        <v>117.9190832</v>
       </c>
       <c r="O17">
-        <v>35.5427109</v>
+        <v>35.37572496</v>
       </c>
       <c r="P17">
-        <v>82.93299210000001</v>
+        <v>82.54335824</v>
       </c>
       <c r="Q17">
-        <v>204.7329921</v>
+        <v>204.34335824</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1389446989054028</v>
+        <v>0.1397574798731637</v>
       </c>
       <c r="T17">
-        <v>0.6494460624063608</v>
+        <v>0.6551131310137461</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.18990161686667</v>
+        <v>14.2405327658125</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1230298830934575</v>
+        <v>0.1226752721173227</v>
       </c>
       <c r="C18">
-        <v>1193.999944558403</v>
+        <v>1188.36993719065</v>
       </c>
       <c r="D18">
-        <v>1178.455944558403</v>
+        <v>1183.891937190651</v>
       </c>
       <c r="E18">
-        <v>-744.2439999999999</v>
+        <v>-733.178</v>
       </c>
       <c r="F18">
-        <v>177.056</v>
+        <v>188.122</v>
       </c>
       <c r="G18">
         <v>192.6</v>
@@ -2763,28 +2763,28 @@
         <v>126.825</v>
       </c>
       <c r="M18">
-        <v>8.905916799999998</v>
+        <v>9.462536599999998</v>
       </c>
       <c r="N18">
-        <v>117.9190832</v>
+        <v>117.3624634</v>
       </c>
       <c r="O18">
-        <v>35.37572496</v>
+        <v>35.20873902</v>
       </c>
       <c r="P18">
-        <v>82.54335824</v>
+        <v>82.15372438</v>
       </c>
       <c r="Q18">
-        <v>204.34335824</v>
+        <v>203.95372438</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1397574798731637</v>
+        <v>0.1405898459244852</v>
       </c>
       <c r="T18">
-        <v>0.6551131310137461</v>
+        <v>0.660916755491189</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.2405327658125</v>
+        <v>13.40285436782353</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1226752721173227</v>
+        <v>0.1225096611411878</v>
       </c>
       <c r="C19">
-        <v>1188.36993719065</v>
+        <v>1179.859879902943</v>
       </c>
       <c r="D19">
-        <v>1183.891937190651</v>
+        <v>1186.447879902944</v>
       </c>
       <c r="E19">
-        <v>-733.178</v>
+        <v>-722.112</v>
       </c>
       <c r="F19">
-        <v>188.122</v>
+        <v>199.188</v>
       </c>
       <c r="G19">
         <v>192.6</v>
@@ -2845,45 +2845,45 @@
         <v>126.825</v>
       </c>
       <c r="M19">
-        <v>9.462536599999998</v>
+        <v>10.3179384</v>
       </c>
       <c r="N19">
-        <v>117.3624634</v>
+        <v>116.5070616</v>
       </c>
       <c r="O19">
-        <v>35.20873902</v>
+        <v>34.95211848</v>
       </c>
       <c r="P19">
-        <v>82.15372438</v>
+        <v>81.55494312</v>
       </c>
       <c r="Q19">
-        <v>203.95372438</v>
+        <v>203.35494312</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1405898459244852</v>
+        <v>0.1414425135868145</v>
       </c>
       <c r="T19">
-        <v>0.660916755491189</v>
+        <v>0.6668619317851547</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.40285436782353</v>
+        <v>12.29169966744519</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1225096611411879</v>
+        <v>0.122165550165053</v>
       </c>
       <c r="C20">
-        <v>1179.859879902944</v>
+        <v>1174.140135344096</v>
       </c>
       <c r="D20">
-        <v>1186.447879902944</v>
+        <v>1191.794135344096</v>
       </c>
       <c r="E20">
-        <v>-722.112</v>
+        <v>-711.0459999999999</v>
       </c>
       <c r="F20">
-        <v>199.188</v>
+        <v>210.254</v>
       </c>
       <c r="G20">
         <v>192.6</v>
@@ -2927,28 +2927,28 @@
         <v>126.825</v>
       </c>
       <c r="M20">
-        <v>10.3179384</v>
+        <v>10.8911572</v>
       </c>
       <c r="N20">
-        <v>116.5070616</v>
+        <v>115.9338428</v>
       </c>
       <c r="O20">
-        <v>34.95211848</v>
+        <v>34.78015284</v>
       </c>
       <c r="P20">
-        <v>81.55494312</v>
+        <v>81.15368996000001</v>
       </c>
       <c r="Q20">
-        <v>203.35494312</v>
+        <v>202.95368996</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1414425135868145</v>
+        <v>0.1423162347716704</v>
       </c>
       <c r="T20">
-        <v>0.6668619317851547</v>
+        <v>0.6729539025555148</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.2916996674452</v>
+        <v>11.64476810600071</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.122165550165053</v>
+        <v>0.1218214391889182</v>
       </c>
       <c r="C21">
-        <v>1174.140135344096</v>
+        <v>1168.468790426143</v>
       </c>
       <c r="D21">
-        <v>1191.794135344096</v>
+        <v>1197.188790426143</v>
       </c>
       <c r="E21">
-        <v>-711.0459999999999</v>
+        <v>-699.98</v>
       </c>
       <c r="F21">
-        <v>210.254</v>
+        <v>221.32</v>
       </c>
       <c r="G21">
         <v>192.6</v>
@@ -3009,28 +3009,28 @@
         <v>126.825</v>
       </c>
       <c r="M21">
-        <v>10.8911572</v>
+        <v>11.464376</v>
       </c>
       <c r="N21">
-        <v>115.9338428</v>
+        <v>115.360624</v>
       </c>
       <c r="O21">
-        <v>34.78015284</v>
+        <v>34.6081872</v>
       </c>
       <c r="P21">
-        <v>81.15368996000001</v>
+        <v>80.7524368</v>
       </c>
       <c r="Q21">
-        <v>202.95368996</v>
+        <v>202.5524368</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1423162347716704</v>
+        <v>0.1432117989861477</v>
       </c>
       <c r="T21">
-        <v>0.6729539025555148</v>
+        <v>0.6791981725951339</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.64476810600071</v>
+        <v>11.06252970070068</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1218214391889182</v>
+        <v>0.1214773282127833</v>
       </c>
       <c r="C22">
-        <v>1168.468790426143</v>
+        <v>1162.846505380415</v>
       </c>
       <c r="D22">
-        <v>1197.188790426143</v>
+        <v>1202.632505380415</v>
       </c>
       <c r="E22">
-        <v>-699.98</v>
+        <v>-688.914</v>
       </c>
       <c r="F22">
-        <v>221.32</v>
+        <v>232.386</v>
       </c>
       <c r="G22">
         <v>192.6</v>
@@ -3091,28 +3091,28 @@
         <v>126.825</v>
       </c>
       <c r="M22">
-        <v>11.464376</v>
+        <v>12.0375948</v>
       </c>
       <c r="N22">
-        <v>115.360624</v>
+        <v>114.7874052</v>
       </c>
       <c r="O22">
-        <v>34.6081872</v>
+        <v>34.43622156</v>
       </c>
       <c r="P22">
-        <v>80.7524368</v>
+        <v>80.35118364000002</v>
       </c>
       <c r="Q22">
-        <v>202.5524368</v>
+        <v>202.15118364</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1432117989861477</v>
+        <v>0.1441300357123839</v>
       </c>
       <c r="T22">
-        <v>0.6791981725951339</v>
+        <v>0.6856005254205662</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.06252970070068</v>
+        <v>10.53574257209588</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1214773282127833</v>
+        <v>0.1211332172366485</v>
       </c>
       <c r="C23">
-        <v>1162.846505380415</v>
+        <v>1157.273952501596</v>
       </c>
       <c r="D23">
-        <v>1202.632505380415</v>
+        <v>1208.125952501596</v>
       </c>
       <c r="E23">
-        <v>-688.914</v>
+        <v>-677.848</v>
       </c>
       <c r="F23">
-        <v>232.386</v>
+        <v>243.452</v>
       </c>
       <c r="G23">
         <v>192.6</v>
@@ -3173,28 +3173,28 @@
         <v>126.825</v>
       </c>
       <c r="M23">
-        <v>12.0375948</v>
+        <v>12.6108136</v>
       </c>
       <c r="N23">
-        <v>114.7874052</v>
+        <v>114.2141864</v>
       </c>
       <c r="O23">
-        <v>34.43622156</v>
+        <v>34.26425592</v>
       </c>
       <c r="P23">
-        <v>80.35118364000002</v>
+        <v>79.94993048000001</v>
       </c>
       <c r="Q23">
-        <v>202.15118364</v>
+        <v>201.74993048</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1441300357123839</v>
+        <v>0.1450718169700621</v>
       </c>
       <c r="T23">
-        <v>0.685600525420566</v>
+        <v>0.692167041138958</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.53574257209588</v>
+        <v>10.05684518245516</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1211332172366485</v>
+        <v>0.1210628062605136</v>
       </c>
       <c r="C24">
-        <v>1157.273952501596</v>
+        <v>1147.338196400754</v>
       </c>
       <c r="D24">
-        <v>1208.125952501596</v>
+        <v>1209.256196400754</v>
       </c>
       <c r="E24">
-        <v>-677.848</v>
+        <v>-666.7819999999999</v>
       </c>
       <c r="F24">
-        <v>243.452</v>
+        <v>254.518</v>
       </c>
       <c r="G24">
         <v>192.6</v>
@@ -3255,45 +3255,45 @@
         <v>126.825</v>
       </c>
       <c r="M24">
-        <v>12.6108136</v>
+        <v>13.616713</v>
       </c>
       <c r="N24">
-        <v>114.2141864</v>
+        <v>113.208287</v>
       </c>
       <c r="O24">
-        <v>34.26425592</v>
+        <v>33.9624861</v>
       </c>
       <c r="P24">
-        <v>79.94993048000001</v>
+        <v>79.24580090000001</v>
       </c>
       <c r="Q24">
-        <v>201.74993048</v>
+        <v>201.0458009</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1450718169700621</v>
+        <v>0.1460380600785891</v>
       </c>
       <c r="T24">
-        <v>0.692167041138958</v>
+        <v>0.6989041157071784</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.05684518245516</v>
+        <v>9.313921795957659</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1210628062605136</v>
+        <v>0.1207305952843788</v>
       </c>
       <c r="C25">
-        <v>1147.338196400754</v>
+        <v>1141.633533513835</v>
       </c>
       <c r="D25">
-        <v>1209.256196400754</v>
+        <v>1214.617533513835</v>
       </c>
       <c r="E25">
-        <v>-666.7819999999999</v>
+        <v>-655.7159999999999</v>
       </c>
       <c r="F25">
-        <v>254.518</v>
+        <v>265.584</v>
       </c>
       <c r="G25">
         <v>192.6</v>
@@ -3337,28 +3337,28 @@
         <v>126.825</v>
       </c>
       <c r="M25">
-        <v>13.616713</v>
+        <v>14.208744</v>
       </c>
       <c r="N25">
-        <v>113.208287</v>
+        <v>112.616256</v>
       </c>
       <c r="O25">
-        <v>33.9624861</v>
+        <v>33.7848768</v>
       </c>
       <c r="P25">
-        <v>79.24580090000001</v>
+        <v>78.83137920000001</v>
       </c>
       <c r="Q25">
-        <v>201.0458009</v>
+        <v>200.6313792</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1460380600785891</v>
+        <v>0.1470297306373405</v>
       </c>
       <c r="T25">
-        <v>0.6989041157071784</v>
+        <v>0.7058184817114045</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.313921795957659</v>
+        <v>8.925841721126091</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1207305952843788</v>
+        <v>0.1203983843082439</v>
       </c>
       <c r="C26">
-        <v>1141.633533513836</v>
+        <v>1135.976622198274</v>
       </c>
       <c r="D26">
-        <v>1214.617533513835</v>
+        <v>1220.026622198274</v>
       </c>
       <c r="E26">
-        <v>-655.716</v>
+        <v>-644.65</v>
       </c>
       <c r="F26">
-        <v>265.5839999999999</v>
+        <v>276.65</v>
       </c>
       <c r="G26">
         <v>192.6</v>
@@ -3419,28 +3419,28 @@
         <v>126.825</v>
       </c>
       <c r="M26">
-        <v>14.208744</v>
+        <v>14.800775</v>
       </c>
       <c r="N26">
-        <v>112.616256</v>
+        <v>112.024225</v>
       </c>
       <c r="O26">
-        <v>33.7848768</v>
+        <v>33.6072675</v>
       </c>
       <c r="P26">
-        <v>78.83137920000001</v>
+        <v>78.4169575</v>
       </c>
       <c r="Q26">
-        <v>200.6313792</v>
+        <v>200.2169575</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1470297306373405</v>
+        <v>0.1480478457443253</v>
       </c>
       <c r="T26">
-        <v>0.7058184817114045</v>
+        <v>0.7129172308090768</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.925841721126091</v>
+        <v>8.568808052281046</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1203983843082439</v>
+        <v>0.1200661733321091</v>
       </c>
       <c r="C27">
-        <v>1135.976622198274</v>
+        <v>1130.368103267865</v>
       </c>
       <c r="D27">
-        <v>1220.026622198274</v>
+        <v>1225.484103267865</v>
       </c>
       <c r="E27">
-        <v>-644.65</v>
+        <v>-633.5839999999999</v>
       </c>
       <c r="F27">
-        <v>276.65</v>
+        <v>287.716</v>
       </c>
       <c r="G27">
         <v>192.6</v>
@@ -3501,28 +3501,28 @@
         <v>126.825</v>
       </c>
       <c r="M27">
-        <v>14.800775</v>
+        <v>15.392806</v>
       </c>
       <c r="N27">
-        <v>112.024225</v>
+        <v>111.432194</v>
       </c>
       <c r="O27">
-        <v>33.6072675</v>
+        <v>33.4296582</v>
       </c>
       <c r="P27">
-        <v>78.4169575</v>
+        <v>78.0025358</v>
       </c>
       <c r="Q27">
-        <v>200.2169575</v>
+        <v>199.8025358</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1480478457443253</v>
+        <v>0.1490934774758231</v>
       </c>
       <c r="T27">
-        <v>0.7129172308090768</v>
+        <v>0.7202078379904697</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.568808052281046</v>
+        <v>8.239238511808699</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1200661733321091</v>
+        <v>0.1197339623559742</v>
       </c>
       <c r="C28">
-        <v>1130.368103267865</v>
+        <v>1124.808629054001</v>
       </c>
       <c r="D28">
-        <v>1225.484103267865</v>
+        <v>1230.990629054001</v>
       </c>
       <c r="E28">
-        <v>-633.5839999999999</v>
+        <v>-622.518</v>
       </c>
       <c r="F28">
-        <v>287.716</v>
+        <v>298.782</v>
       </c>
       <c r="G28">
         <v>192.6</v>
@@ -3583,28 +3583,28 @@
         <v>126.825</v>
       </c>
       <c r="M28">
-        <v>15.392806</v>
+        <v>15.984837</v>
       </c>
       <c r="N28">
-        <v>111.432194</v>
+        <v>110.840163</v>
       </c>
       <c r="O28">
-        <v>33.4296582</v>
+        <v>33.2520489</v>
       </c>
       <c r="P28">
-        <v>78.0025358</v>
+        <v>77.58811410000001</v>
       </c>
       <c r="Q28">
-        <v>199.8025358</v>
+        <v>199.3881141</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1490934774758231</v>
+        <v>0.1501677566520195</v>
       </c>
       <c r="T28">
-        <v>0.7202078379904697</v>
+        <v>0.7276981878343668</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.239238511808699</v>
+        <v>7.934081529889858</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1197339623559742</v>
+        <v>0.1194017513798394</v>
       </c>
       <c r="C29">
-        <v>1124.808629054001</v>
+        <v>1119.298863665599</v>
       </c>
       <c r="D29">
-        <v>1230.990629054001</v>
+        <v>1236.546863665599</v>
       </c>
       <c r="E29">
-        <v>-622.518</v>
+        <v>-611.452</v>
       </c>
       <c r="F29">
-        <v>298.782</v>
+        <v>309.848</v>
       </c>
       <c r="G29">
         <v>192.6</v>
@@ -3665,28 +3665,28 @@
         <v>126.825</v>
       </c>
       <c r="M29">
-        <v>15.984837</v>
+        <v>16.576868</v>
       </c>
       <c r="N29">
-        <v>110.840163</v>
+        <v>110.248132</v>
       </c>
       <c r="O29">
-        <v>33.2520489</v>
+        <v>33.0744396</v>
       </c>
       <c r="P29">
-        <v>77.58811410000001</v>
+        <v>77.17369239999999</v>
       </c>
       <c r="Q29">
-        <v>199.3881141</v>
+        <v>198.9736924</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1501677566520195</v>
+        <v>0.1512718769164436</v>
       </c>
       <c r="T29">
-        <v>0.7276981878343668</v>
+        <v>0.7353966029517052</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.934081529889858</v>
+        <v>7.650721475250934</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1194017513798394</v>
+        <v>0.1192319404037046</v>
       </c>
       <c r="C30">
-        <v>1119.298863665599</v>
+        <v>1111.092371787012</v>
       </c>
       <c r="D30">
-        <v>1236.546863665599</v>
+        <v>1239.406371787012</v>
       </c>
       <c r="E30">
-        <v>-611.452</v>
+        <v>-600.386</v>
       </c>
       <c r="F30">
-        <v>309.848</v>
+        <v>320.914</v>
       </c>
       <c r="G30">
         <v>192.6</v>
@@ -3747,45 +3747,45 @@
         <v>126.825</v>
       </c>
       <c r="M30">
-        <v>16.576868</v>
+        <v>17.4256302</v>
       </c>
       <c r="N30">
-        <v>110.248132</v>
+        <v>109.3993698</v>
       </c>
       <c r="O30">
-        <v>33.0744396</v>
+        <v>32.81981094</v>
       </c>
       <c r="P30">
-        <v>77.17369239999999</v>
+        <v>76.57955886000001</v>
       </c>
       <c r="Q30">
-        <v>198.9736924</v>
+        <v>198.37955886</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1512718769164436</v>
+        <v>0.1524070991601473</v>
       </c>
       <c r="T30">
-        <v>0.7353966029517052</v>
+        <v>0.7433118748329125</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.650721475250934</v>
+        <v>7.278072502651869</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1192319404037046</v>
+        <v>0.1189053294275697</v>
       </c>
       <c r="C31">
-        <v>1111.092371787012</v>
+        <v>1105.563638742606</v>
       </c>
       <c r="D31">
-        <v>1239.406371787012</v>
+        <v>1244.943638742606</v>
       </c>
       <c r="E31">
-        <v>-600.386</v>
+        <v>-589.3199999999999</v>
       </c>
       <c r="F31">
-        <v>320.9139999999999</v>
+        <v>331.98</v>
       </c>
       <c r="G31">
         <v>192.6</v>
@@ -3829,28 +3829,28 @@
         <v>126.825</v>
       </c>
       <c r="M31">
-        <v>17.4256302</v>
+        <v>18.026514</v>
       </c>
       <c r="N31">
-        <v>109.3993698</v>
+        <v>108.798486</v>
       </c>
       <c r="O31">
-        <v>32.81981094</v>
+        <v>32.6395458</v>
       </c>
       <c r="P31">
-        <v>76.57955886000001</v>
+        <v>76.15894019999999</v>
       </c>
       <c r="Q31">
-        <v>198.37955886</v>
+        <v>197.9589402</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1524070991601473</v>
+        <v>0.1535747563250996</v>
       </c>
       <c r="T31">
-        <v>0.7433118748329125</v>
+        <v>0.7514532973392971</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.278072502651871</v>
+        <v>7.035470085896808</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1189053294275697</v>
+        <v>0.1185787184514348</v>
       </c>
       <c r="C32">
-        <v>1105.563638742606</v>
+        <v>1100.084605176399</v>
       </c>
       <c r="D32">
-        <v>1244.943638742606</v>
+        <v>1250.530605176399</v>
       </c>
       <c r="E32">
-        <v>-589.3199999999999</v>
+        <v>-578.2539999999999</v>
       </c>
       <c r="F32">
-        <v>331.98</v>
+        <v>343.046</v>
       </c>
       <c r="G32">
         <v>192.6</v>
@@ -3911,28 +3911,28 @@
         <v>126.825</v>
       </c>
       <c r="M32">
-        <v>18.026514</v>
+        <v>18.6273978</v>
       </c>
       <c r="N32">
-        <v>108.798486</v>
+        <v>108.1976022</v>
       </c>
       <c r="O32">
-        <v>32.6395458</v>
+        <v>32.45928066</v>
       </c>
       <c r="P32">
-        <v>76.15894019999999</v>
+        <v>75.73832154000002</v>
       </c>
       <c r="Q32">
-        <v>197.9589402</v>
+        <v>197.53832154</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1535747563250996</v>
+        <v>0.1547762586252679</v>
       </c>
       <c r="T32">
-        <v>0.7514532973392971</v>
+        <v>0.7598307031067362</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.035470085896808</v>
+        <v>6.808519437964653</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1185787184514348</v>
+        <v>0.1182521074753</v>
       </c>
       <c r="C33">
-        <v>1100.084605176399</v>
+        <v>1094.655943217703</v>
       </c>
       <c r="D33">
-        <v>1250.530605176399</v>
+        <v>1256.167943217703</v>
       </c>
       <c r="E33">
-        <v>-578.2539999999999</v>
+        <v>-567.188</v>
       </c>
       <c r="F33">
-        <v>343.046</v>
+        <v>354.112</v>
       </c>
       <c r="G33">
         <v>192.6</v>
@@ -3993,28 +3993,28 @@
         <v>126.825</v>
       </c>
       <c r="M33">
-        <v>18.6273978</v>
+        <v>19.2282816</v>
       </c>
       <c r="N33">
-        <v>108.1976022</v>
+        <v>107.5967184</v>
       </c>
       <c r="O33">
-        <v>32.45928066</v>
+        <v>32.27901552</v>
       </c>
       <c r="P33">
-        <v>75.73832154000002</v>
+        <v>75.31770288</v>
       </c>
       <c r="Q33">
-        <v>197.53832154</v>
+        <v>197.11770288</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1547762586252679</v>
+        <v>0.1560130992283824</v>
       </c>
       <c r="T33">
-        <v>0.7598307031067362</v>
+        <v>0.768454503161453</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.808519437964653</v>
+        <v>6.595753205528257</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1182521074753</v>
+        <v>0.1179254964991652</v>
       </c>
       <c r="C34">
-        <v>1094.655943217703</v>
+        <v>1089.278337170434</v>
       </c>
       <c r="D34">
-        <v>1256.167943217703</v>
+        <v>1261.856337170435</v>
       </c>
       <c r="E34">
-        <v>-567.188</v>
+        <v>-556.122</v>
       </c>
       <c r="F34">
-        <v>354.112</v>
+        <v>365.178</v>
       </c>
       <c r="G34">
         <v>192.6</v>
@@ -4075,28 +4075,28 @@
         <v>126.825</v>
       </c>
       <c r="M34">
-        <v>19.2282816</v>
+        <v>19.8291654</v>
       </c>
       <c r="N34">
-        <v>107.5967184</v>
+        <v>106.9958346</v>
       </c>
       <c r="O34">
-        <v>32.27901552</v>
+        <v>32.09875038</v>
       </c>
       <c r="P34">
-        <v>75.31770288</v>
+        <v>74.89708422</v>
       </c>
       <c r="Q34">
-        <v>197.11770288</v>
+        <v>196.69708422</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1560130992283824</v>
+        <v>0.1572868604465152</v>
       </c>
       <c r="T34">
-        <v>0.768454503161453</v>
+        <v>0.777335730083475</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.595753205528257</v>
+        <v>6.395881896269825</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1179254964991652</v>
+        <v>0.1175988855230303</v>
       </c>
       <c r="C35">
-        <v>1089.278337170434</v>
+        <v>1083.952483790022</v>
       </c>
       <c r="D35">
-        <v>1261.856337170435</v>
+        <v>1267.596483790022</v>
       </c>
       <c r="E35">
-        <v>-556.122</v>
+        <v>-545.056</v>
       </c>
       <c r="F35">
-        <v>365.178</v>
+        <v>376.244</v>
       </c>
       <c r="G35">
         <v>192.6</v>
@@ -4157,28 +4157,28 @@
         <v>126.825</v>
       </c>
       <c r="M35">
-        <v>19.8291654</v>
+        <v>20.4300492</v>
       </c>
       <c r="N35">
-        <v>106.9958346</v>
+        <v>106.3949508</v>
       </c>
       <c r="O35">
-        <v>32.09875038</v>
+        <v>31.91848524</v>
       </c>
       <c r="P35">
-        <v>74.89708422</v>
+        <v>74.47646556000001</v>
       </c>
       <c r="Q35">
-        <v>196.69708422</v>
+        <v>196.27646556</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1572868604465152</v>
+        <v>0.1585992204894399</v>
       </c>
       <c r="T35">
-        <v>0.777335730083475</v>
+        <v>0.7864860850940428</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.395881896269825</v>
+        <v>6.207767722850124</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1175988855230303</v>
+        <v>0.1175172745468955</v>
       </c>
       <c r="C36">
-        <v>1083.952483790022</v>
+        <v>1074.328950574221</v>
       </c>
       <c r="D36">
-        <v>1267.596483790022</v>
+        <v>1269.038950574221</v>
       </c>
       <c r="E36">
-        <v>-545.056</v>
+        <v>-533.99</v>
       </c>
       <c r="F36">
-        <v>376.244</v>
+        <v>387.31</v>
       </c>
       <c r="G36">
         <v>192.6</v>
@@ -4239,45 +4239,45 @@
         <v>126.825</v>
       </c>
       <c r="M36">
-        <v>20.4300492</v>
+        <v>21.418243</v>
       </c>
       <c r="N36">
-        <v>106.3949508</v>
+        <v>105.406757</v>
       </c>
       <c r="O36">
-        <v>31.91848524</v>
+        <v>31.6220271</v>
       </c>
       <c r="P36">
-        <v>74.47646556000001</v>
+        <v>73.7847299</v>
       </c>
       <c r="Q36">
-        <v>196.27646556</v>
+        <v>195.5847299</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1585992204894399</v>
+        <v>0.1599519608413777</v>
       </c>
       <c r="T36">
-        <v>0.7864860850940428</v>
+        <v>0.7959179894895513</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.207767722850124</v>
+        <v>5.921354053177938</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1175172745468955</v>
+        <v>0.1171976635707606</v>
       </c>
       <c r="C37">
-        <v>1074.328950574221</v>
+        <v>1068.943791619449</v>
       </c>
       <c r="D37">
-        <v>1269.038950574221</v>
+        <v>1274.71979161945</v>
       </c>
       <c r="E37">
-        <v>-533.99</v>
+        <v>-522.924</v>
       </c>
       <c r="F37">
-        <v>387.31</v>
+        <v>398.376</v>
       </c>
       <c r="G37">
         <v>192.6</v>
@@ -4321,28 +4321,28 @@
         <v>126.825</v>
       </c>
       <c r="M37">
-        <v>21.418243</v>
+        <v>22.0301928</v>
       </c>
       <c r="N37">
-        <v>105.406757</v>
+        <v>104.7948072</v>
       </c>
       <c r="O37">
-        <v>31.6220271</v>
+        <v>31.43844216</v>
       </c>
       <c r="P37">
-        <v>73.7847299</v>
+        <v>73.35636504000001</v>
       </c>
       <c r="Q37">
-        <v>195.5847299</v>
+        <v>195.15636504</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1599519608413777</v>
+        <v>0.1613469743293135</v>
       </c>
       <c r="T37">
-        <v>0.7959179894895513</v>
+        <v>0.8056446408974195</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.921354053177938</v>
+        <v>5.756871996145217</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1171976635707606</v>
+        <v>0.1168780525946258</v>
       </c>
       <c r="C38">
-        <v>1068.943791619449</v>
+        <v>1063.609721828926</v>
       </c>
       <c r="D38">
-        <v>1274.71979161945</v>
+        <v>1280.451721828926</v>
       </c>
       <c r="E38">
-        <v>-522.924</v>
+        <v>-511.858</v>
       </c>
       <c r="F38">
-        <v>398.376</v>
+        <v>409.442</v>
       </c>
       <c r="G38">
         <v>192.6</v>
@@ -4403,28 +4403,28 @@
         <v>126.825</v>
       </c>
       <c r="M38">
-        <v>22.0301928</v>
+        <v>22.6421426</v>
       </c>
       <c r="N38">
-        <v>104.7948072</v>
+        <v>104.1828574</v>
       </c>
       <c r="O38">
-        <v>31.43844216</v>
+        <v>31.25485722</v>
       </c>
       <c r="P38">
-        <v>73.35636504000001</v>
+        <v>72.92800018</v>
       </c>
       <c r="Q38">
-        <v>195.15636504</v>
+        <v>194.72800018</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1613469743293135</v>
+        <v>0.1627862739597235</v>
       </c>
       <c r="T38">
-        <v>0.8056446408974195</v>
+        <v>0.8156800748896642</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.756871996145218</v>
+        <v>5.601280861114266</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1168780525946258</v>
+        <v>0.1165584416184909</v>
       </c>
       <c r="C39">
-        <v>1063.609721828926</v>
+        <v>1058.327433501292</v>
       </c>
       <c r="D39">
-        <v>1280.451721828926</v>
+        <v>1286.235433501292</v>
       </c>
       <c r="E39">
-        <v>-511.858</v>
+        <v>-500.792</v>
       </c>
       <c r="F39">
-        <v>409.442</v>
+        <v>420.508</v>
       </c>
       <c r="G39">
         <v>192.6</v>
@@ -4485,28 +4485,28 @@
         <v>126.825</v>
       </c>
       <c r="M39">
-        <v>22.6421426</v>
+        <v>23.2540924</v>
       </c>
       <c r="N39">
-        <v>104.1828574</v>
+        <v>103.5709076</v>
       </c>
       <c r="O39">
-        <v>31.25485722</v>
+        <v>31.07127228</v>
       </c>
       <c r="P39">
-        <v>72.92800018</v>
+        <v>72.49963532</v>
       </c>
       <c r="Q39">
-        <v>194.72800018</v>
+        <v>194.29963532</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1627862739597235</v>
+        <v>0.1642720026104693</v>
       </c>
       <c r="T39">
-        <v>0.8156800748896642</v>
+        <v>0.8260392325590784</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.601280861114266</v>
+        <v>5.453878733190206</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1165584416184909</v>
+        <v>0.1162388306423561</v>
       </c>
       <c r="C40">
-        <v>1058.327433501292</v>
+        <v>1053.097631500204</v>
       </c>
       <c r="D40">
-        <v>1286.235433501292</v>
+        <v>1292.071631500203</v>
       </c>
       <c r="E40">
-        <v>-500.792</v>
+        <v>-489.726</v>
       </c>
       <c r="F40">
-        <v>420.508</v>
+        <v>431.574</v>
       </c>
       <c r="G40">
         <v>192.6</v>
@@ -4567,28 +4567,28 @@
         <v>126.825</v>
       </c>
       <c r="M40">
-        <v>23.2540924</v>
+        <v>23.8660422</v>
       </c>
       <c r="N40">
-        <v>103.5709076</v>
+        <v>102.9589578</v>
       </c>
       <c r="O40">
-        <v>31.07127228</v>
+        <v>30.88768734</v>
       </c>
       <c r="P40">
-        <v>72.49963532</v>
+        <v>72.07127046000001</v>
       </c>
       <c r="Q40">
-        <v>194.29963532</v>
+        <v>193.87127046</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1642720026104693</v>
+        <v>0.1658064436759936</v>
       </c>
       <c r="T40">
-        <v>0.8260392325590784</v>
+        <v>0.8367380347422437</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.453878733190206</v>
+        <v>5.314035688749432</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1162388306423561</v>
+        <v>0.1159192196662213</v>
       </c>
       <c r="C41">
-        <v>1053.097631500204</v>
+        <v>1047.921033540694</v>
       </c>
       <c r="D41">
-        <v>1292.071631500203</v>
+        <v>1297.961033540694</v>
       </c>
       <c r="E41">
-        <v>-489.726</v>
+        <v>-478.66</v>
       </c>
       <c r="F41">
-        <v>431.574</v>
+        <v>442.64</v>
       </c>
       <c r="G41">
         <v>192.6</v>
@@ -4649,28 +4649,28 @@
         <v>126.825</v>
       </c>
       <c r="M41">
-        <v>23.8660422</v>
+        <v>24.477992</v>
       </c>
       <c r="N41">
-        <v>102.9589578</v>
+        <v>102.347008</v>
       </c>
       <c r="O41">
-        <v>30.88768734</v>
+        <v>30.7041024</v>
       </c>
       <c r="P41">
-        <v>72.07127046000001</v>
+        <v>71.64290560000001</v>
       </c>
       <c r="Q41">
-        <v>193.87127046</v>
+        <v>193.4429056</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1658064436759936</v>
+        <v>0.1673920327770355</v>
       </c>
       <c r="T41">
-        <v>0.8367380347422437</v>
+        <v>0.8477934636648481</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.314035688749432</v>
+        <v>5.181184796530696</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1159192196662213</v>
+        <v>0.1155996086900864</v>
       </c>
       <c r="C42">
-        <v>1047.921033540694</v>
+        <v>1042.798370483411</v>
       </c>
       <c r="D42">
-        <v>1297.961033540694</v>
+        <v>1303.904370483411</v>
       </c>
       <c r="E42">
-        <v>-478.66</v>
+        <v>-467.5939999999999</v>
       </c>
       <c r="F42">
-        <v>442.64</v>
+        <v>453.706</v>
       </c>
       <c r="G42">
         <v>192.6</v>
@@ -4731,28 +4731,28 @@
         <v>126.825</v>
       </c>
       <c r="M42">
-        <v>24.477992</v>
+        <v>25.0899418</v>
       </c>
       <c r="N42">
-        <v>102.347008</v>
+        <v>101.7350582</v>
       </c>
       <c r="O42">
-        <v>30.7041024</v>
+        <v>30.52051746</v>
       </c>
       <c r="P42">
-        <v>71.64290560000001</v>
+        <v>71.21454074</v>
       </c>
       <c r="Q42">
-        <v>193.4429056</v>
+        <v>193.01454074</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1673920327770355</v>
+        <v>0.1690313706611634</v>
       </c>
       <c r="T42">
-        <v>0.8477934636648481</v>
+        <v>0.8592236528899133</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.181184796530696</v>
+        <v>5.054814435639702</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1155996086900864</v>
+        <v>0.1152799977139516</v>
       </c>
       <c r="C43">
-        <v>1042.798370483411</v>
+        <v>1037.730386636958</v>
       </c>
       <c r="D43">
-        <v>1303.904370483411</v>
+        <v>1309.902386636958</v>
       </c>
       <c r="E43">
-        <v>-467.5939999999999</v>
+        <v>-456.528</v>
       </c>
       <c r="F43">
-        <v>453.706</v>
+        <v>464.772</v>
       </c>
       <c r="G43">
         <v>192.6</v>
@@ -4813,28 +4813,28 @@
         <v>126.825</v>
       </c>
       <c r="M43">
-        <v>25.0899418</v>
+        <v>25.7018916</v>
       </c>
       <c r="N43">
-        <v>101.7350582</v>
+        <v>101.1231084</v>
       </c>
       <c r="O43">
-        <v>30.52051746</v>
+        <v>30.33693252</v>
       </c>
       <c r="P43">
-        <v>71.21454074</v>
+        <v>70.78617588</v>
       </c>
       <c r="Q43">
-        <v>193.01454074</v>
+        <v>192.58617588</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1690313706611634</v>
+        <v>0.1707272374378475</v>
       </c>
       <c r="T43">
-        <v>0.8592236528899133</v>
+        <v>0.8710479865710155</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.054814435639702</v>
+        <v>4.934461710981616</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1152799977139516</v>
+        <v>0.1149603867378167</v>
       </c>
       <c r="C44">
-        <v>1037.730386636958</v>
+        <v>1032.717840068638</v>
       </c>
       <c r="D44">
-        <v>1309.902386636958</v>
+        <v>1315.955840068639</v>
       </c>
       <c r="E44">
-        <v>-456.528</v>
+        <v>-445.462</v>
       </c>
       <c r="F44">
-        <v>464.7719999999999</v>
+        <v>475.838</v>
       </c>
       <c r="G44">
         <v>192.6</v>
@@ -4895,28 +4895,28 @@
         <v>126.825</v>
       </c>
       <c r="M44">
-        <v>25.7018916</v>
+        <v>26.3138414</v>
       </c>
       <c r="N44">
-        <v>101.1231084</v>
+        <v>100.5111586</v>
       </c>
       <c r="O44">
-        <v>30.33693252</v>
+        <v>30.15334758</v>
       </c>
       <c r="P44">
-        <v>70.78617588</v>
+        <v>70.35781102</v>
       </c>
       <c r="Q44">
-        <v>192.58617588</v>
+        <v>192.15781102</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1707272374378475</v>
+        <v>0.1724826083119592</v>
       </c>
       <c r="T44">
-        <v>0.8710479865710153</v>
+        <v>0.8832872091532088</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.934461710981616</v>
+        <v>4.819706787470415</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1149603867378167</v>
+        <v>0.1146407757616819</v>
       </c>
       <c r="C45">
-        <v>1032.717840068638</v>
+        <v>1027.761502923844</v>
       </c>
       <c r="D45">
-        <v>1315.955840068639</v>
+        <v>1322.065502923844</v>
       </c>
       <c r="E45">
-        <v>-445.462</v>
+        <v>-434.396</v>
       </c>
       <c r="F45">
-        <v>475.838</v>
+        <v>486.9039999999999</v>
       </c>
       <c r="G45">
         <v>192.6</v>
@@ -4977,28 +4977,28 @@
         <v>126.825</v>
       </c>
       <c r="M45">
-        <v>26.3138414</v>
+        <v>26.9257912</v>
       </c>
       <c r="N45">
-        <v>100.5111586</v>
+        <v>99.8992088</v>
       </c>
       <c r="O45">
-        <v>30.15334758</v>
+        <v>29.96976264</v>
       </c>
       <c r="P45">
-        <v>70.35781102</v>
+        <v>69.92944616</v>
       </c>
       <c r="Q45">
-        <v>192.15781102</v>
+        <v>191.72944616</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1724826083119592</v>
+        <v>0.1743006710030033</v>
       </c>
       <c r="T45">
-        <v>0.8832872091532088</v>
+        <v>0.8959635468276234</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.819706787470415</v>
+        <v>4.710167996846087</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1146407757616819</v>
+        <v>0.114321164785547</v>
       </c>
       <c r="C46">
-        <v>1027.761502923844</v>
+        <v>1022.862161754384</v>
       </c>
       <c r="D46">
-        <v>1322.065502923844</v>
+        <v>1328.232161754384</v>
       </c>
       <c r="E46">
-        <v>-434.396</v>
+        <v>-423.33</v>
       </c>
       <c r="F46">
-        <v>486.9039999999999</v>
+        <v>497.97</v>
       </c>
       <c r="G46">
         <v>192.6</v>
@@ -5059,28 +5059,28 @@
         <v>126.825</v>
       </c>
       <c r="M46">
-        <v>26.9257912</v>
+        <v>27.537741</v>
       </c>
       <c r="N46">
-        <v>99.8992088</v>
+        <v>99.28725900000001</v>
       </c>
       <c r="O46">
-        <v>29.96976264</v>
+        <v>29.7861777</v>
       </c>
       <c r="P46">
-        <v>69.92944616</v>
+        <v>69.50108130000001</v>
       </c>
       <c r="Q46">
-        <v>191.72944616</v>
+        <v>191.3010813</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1743006710030033</v>
+        <v>0.176184845064631</v>
       </c>
       <c r="T46">
-        <v>0.8959635468276234</v>
+        <v>0.9091008422356531</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.710167996846087</v>
+        <v>4.605497596916174</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.114321164785547</v>
+        <v>0.1140015538094122</v>
       </c>
       <c r="C47">
-        <v>1022.862161754384</v>
+        <v>1018.020617856049</v>
       </c>
       <c r="D47">
-        <v>1328.232161754384</v>
+        <v>1334.456617856049</v>
       </c>
       <c r="E47">
-        <v>-423.33</v>
+        <v>-412.264</v>
       </c>
       <c r="F47">
-        <v>497.97</v>
+        <v>509.036</v>
       </c>
       <c r="G47">
         <v>192.6</v>
@@ -5141,28 +5141,28 @@
         <v>126.825</v>
       </c>
       <c r="M47">
-        <v>27.537741</v>
+        <v>28.1496908</v>
       </c>
       <c r="N47">
-        <v>99.28725900000001</v>
+        <v>98.6753092</v>
       </c>
       <c r="O47">
-        <v>29.7861777</v>
+        <v>29.60259276</v>
       </c>
       <c r="P47">
-        <v>69.50108130000001</v>
+        <v>69.07271643999999</v>
       </c>
       <c r="Q47">
-        <v>191.3010813</v>
+        <v>190.87271644</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.176184845064631</v>
+        <v>0.1781388033507633</v>
       </c>
       <c r="T47">
-        <v>0.9091008422356531</v>
+        <v>0.9227247041402763</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.605497596916174</v>
+        <v>4.505378083939735</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1140015538094122</v>
+        <v>0.1145044428332773</v>
       </c>
       <c r="C48">
-        <v>1018.020617856049</v>
+        <v>997.1869295047658</v>
       </c>
       <c r="D48">
-        <v>1334.456617856049</v>
+        <v>1324.688929504766</v>
       </c>
       <c r="E48">
-        <v>-412.264</v>
+        <v>-401.198</v>
       </c>
       <c r="F48">
-        <v>509.036</v>
+        <v>520.102</v>
       </c>
       <c r="G48">
         <v>192.6</v>
@@ -5223,45 +5223,45 @@
         <v>126.825</v>
       </c>
       <c r="M48">
-        <v>28.1496908</v>
+        <v>30.0618956</v>
       </c>
       <c r="N48">
-        <v>98.6753092</v>
+        <v>96.7631044</v>
       </c>
       <c r="O48">
-        <v>29.60259276</v>
+        <v>29.02893132</v>
       </c>
       <c r="P48">
-        <v>69.07271643999999</v>
+        <v>67.73417308000001</v>
       </c>
       <c r="Q48">
-        <v>190.87271644</v>
+        <v>189.53417308</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1781388033507633</v>
+        <v>0.180166495911844</v>
       </c>
       <c r="T48">
-        <v>0.9227247041402763</v>
+        <v>0.9368626740413006</v>
       </c>
       <c r="U48">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.505378083939735</v>
+        <v>4.218795836680372</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1145044428332773</v>
+        <v>0.1142023318571425</v>
       </c>
       <c r="C49">
-        <v>997.1869295047658</v>
+        <v>991.9716520562066</v>
       </c>
       <c r="D49">
-        <v>1324.688929504766</v>
+        <v>1330.539652056207</v>
       </c>
       <c r="E49">
-        <v>-401.198</v>
+        <v>-390.1319999999999</v>
       </c>
       <c r="F49">
-        <v>520.102</v>
+        <v>531.168</v>
       </c>
       <c r="G49">
         <v>192.6</v>
@@ -5305,28 +5305,28 @@
         <v>126.825</v>
       </c>
       <c r="M49">
-        <v>30.0618956</v>
+        <v>30.7015104</v>
       </c>
       <c r="N49">
-        <v>96.7631044</v>
+        <v>96.1234896</v>
       </c>
       <c r="O49">
-        <v>29.02893132</v>
+        <v>28.83704688</v>
       </c>
       <c r="P49">
-        <v>67.73417308000001</v>
+        <v>67.28644272</v>
       </c>
       <c r="Q49">
-        <v>189.53417308</v>
+        <v>189.08644272</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.180166495911844</v>
+        <v>0.182272176648351</v>
       </c>
       <c r="T49">
-        <v>0.9368626740413006</v>
+        <v>0.9515444120154413</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.218795836680372</v>
+        <v>4.130904256749531</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1142023318571425</v>
+        <v>0.1139002208810077</v>
       </c>
       <c r="C50">
-        <v>991.9716520562067</v>
+        <v>986.8082853791027</v>
       </c>
       <c r="D50">
-        <v>1330.539652056207</v>
+        <v>1336.442285379103</v>
       </c>
       <c r="E50">
-        <v>-390.1320000000001</v>
+        <v>-379.066</v>
       </c>
       <c r="F50">
-        <v>531.1679999999999</v>
+        <v>542.2339999999999</v>
       </c>
       <c r="G50">
         <v>192.6</v>
@@ -5387,28 +5387,28 @@
         <v>126.825</v>
       </c>
       <c r="M50">
-        <v>30.7015104</v>
+        <v>31.3411252</v>
       </c>
       <c r="N50">
-        <v>96.1234896</v>
+        <v>95.48387480000001</v>
       </c>
       <c r="O50">
-        <v>28.83704688</v>
+        <v>28.64516244</v>
       </c>
       <c r="P50">
-        <v>67.28644272</v>
+        <v>66.83871236</v>
       </c>
       <c r="Q50">
-        <v>189.08644272</v>
+        <v>188.63871236</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.182272176648351</v>
+        <v>0.184460433100015</v>
       </c>
       <c r="T50">
-        <v>0.9515444120154413</v>
+        <v>0.9668019044199402</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.130904256749531</v>
+        <v>4.046600088244439</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1139002208810077</v>
+        <v>0.1148231099048728</v>
       </c>
       <c r="C51">
-        <v>986.8082853791027</v>
+        <v>957.8730830509912</v>
       </c>
       <c r="D51">
-        <v>1336.442285379103</v>
+        <v>1318.573083050991</v>
       </c>
       <c r="E51">
-        <v>-379.066</v>
+        <v>-368</v>
       </c>
       <c r="F51">
-        <v>542.2339999999999</v>
+        <v>553.3</v>
       </c>
       <c r="G51">
         <v>192.6</v>
@@ -5469,45 +5469,45 @@
         <v>126.825</v>
       </c>
       <c r="M51">
-        <v>31.3411252</v>
+        <v>33.91728999999999</v>
       </c>
       <c r="N51">
-        <v>95.48387480000001</v>
+        <v>92.90771000000001</v>
       </c>
       <c r="O51">
-        <v>28.64516244</v>
+        <v>27.872313</v>
       </c>
       <c r="P51">
-        <v>66.83871236</v>
+        <v>65.035397</v>
       </c>
       <c r="Q51">
-        <v>188.63871236</v>
+        <v>186.835397</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.184460433100015</v>
+        <v>0.1867362198097456</v>
       </c>
       <c r="T51">
-        <v>0.9668019044199402</v>
+        <v>0.9826696965206192</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.046600088244439</v>
+        <v>3.739243318083492</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1148231099048728</v>
+        <v>0.114545498928738</v>
       </c>
       <c r="C52">
-        <v>957.8730830509912</v>
+        <v>952.131800543701</v>
       </c>
       <c r="D52">
-        <v>1318.573083050991</v>
+        <v>1323.897800543701</v>
       </c>
       <c r="E52">
-        <v>-368</v>
+        <v>-356.934</v>
       </c>
       <c r="F52">
-        <v>553.3</v>
+        <v>564.366</v>
       </c>
       <c r="G52">
         <v>192.6</v>
@@ -5551,28 +5551,28 @@
         <v>126.825</v>
       </c>
       <c r="M52">
-        <v>33.91728999999999</v>
+        <v>34.5956358</v>
       </c>
       <c r="N52">
-        <v>92.90771000000001</v>
+        <v>92.22936420000001</v>
       </c>
       <c r="O52">
-        <v>27.872313</v>
+        <v>27.66880926</v>
       </c>
       <c r="P52">
-        <v>65.035397</v>
+        <v>64.56055494</v>
       </c>
       <c r="Q52">
-        <v>186.835397</v>
+        <v>186.36055494</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1867362198097456</v>
+        <v>0.1891048957729346</v>
       </c>
       <c r="T52">
-        <v>0.9826696965206192</v>
+        <v>0.9991851536049995</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.739243318083492</v>
+        <v>3.665924821650481</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.114545498928738</v>
+        <v>0.1142678879526031</v>
       </c>
       <c r="C53">
-        <v>952.131800543701</v>
+        <v>946.4336974031185</v>
       </c>
       <c r="D53">
-        <v>1323.897800543701</v>
+        <v>1329.265697403119</v>
       </c>
       <c r="E53">
-        <v>-356.934</v>
+        <v>-345.8679999999999</v>
       </c>
       <c r="F53">
-        <v>564.366</v>
+        <v>575.432</v>
       </c>
       <c r="G53">
         <v>192.6</v>
@@ -5633,28 +5633,28 @@
         <v>126.825</v>
       </c>
       <c r="M53">
-        <v>34.5956358</v>
+        <v>35.2739816</v>
       </c>
       <c r="N53">
-        <v>92.22936420000001</v>
+        <v>91.5510184</v>
       </c>
       <c r="O53">
-        <v>27.66880926</v>
+        <v>27.46530552</v>
       </c>
       <c r="P53">
-        <v>64.56055494</v>
+        <v>64.08571288</v>
       </c>
       <c r="Q53">
-        <v>186.36055494</v>
+        <v>185.88571288</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1891048957729346</v>
+        <v>0.1915722665679232</v>
       </c>
       <c r="T53">
-        <v>0.9991851536049995</v>
+        <v>1.016388754734562</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.665924821650481</v>
+        <v>3.595426267387972</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1142678879526031</v>
+        <v>0.1139902769764683</v>
       </c>
       <c r="C54">
-        <v>946.4336974031185</v>
+        <v>940.7793009947274</v>
       </c>
       <c r="D54">
-        <v>1329.265697403119</v>
+        <v>1334.677300994727</v>
       </c>
       <c r="E54">
-        <v>-345.8679999999999</v>
+        <v>-334.802</v>
       </c>
       <c r="F54">
-        <v>575.432</v>
+        <v>586.4979999999999</v>
       </c>
       <c r="G54">
         <v>192.6</v>
@@ -5715,28 +5715,28 @@
         <v>126.825</v>
       </c>
       <c r="M54">
-        <v>35.2739816</v>
+        <v>35.95232739999999</v>
       </c>
       <c r="N54">
-        <v>91.5510184</v>
+        <v>90.87267260000002</v>
       </c>
       <c r="O54">
-        <v>27.46530552</v>
+        <v>27.26180178</v>
       </c>
       <c r="P54">
-        <v>64.08571288</v>
+        <v>63.61087082000002</v>
       </c>
       <c r="Q54">
-        <v>185.88571288</v>
+        <v>185.41087082</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1915722665679232</v>
+        <v>0.1941446318648261</v>
       </c>
       <c r="T54">
-        <v>1.016388754734562</v>
+        <v>1.034324423997298</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.595426267387972</v>
+        <v>3.527588035927822</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1139902769764683</v>
+        <v>0.1147710660003334</v>
       </c>
       <c r="C55">
-        <v>940.7793009947274</v>
+        <v>914.6040465283162</v>
       </c>
       <c r="D55">
-        <v>1334.677300994727</v>
+        <v>1319.568046528316</v>
       </c>
       <c r="E55">
-        <v>-334.802</v>
+        <v>-323.736</v>
       </c>
       <c r="F55">
-        <v>586.4979999999999</v>
+        <v>597.564</v>
       </c>
       <c r="G55">
         <v>192.6</v>
@@ -5797,45 +5797,45 @@
         <v>126.825</v>
       </c>
       <c r="M55">
-        <v>35.95232739999999</v>
+        <v>38.3038524</v>
       </c>
       <c r="N55">
-        <v>90.87267260000002</v>
+        <v>88.52114760000001</v>
       </c>
       <c r="O55">
-        <v>27.26180178</v>
+        <v>26.55634428</v>
       </c>
       <c r="P55">
-        <v>63.61087082000002</v>
+        <v>61.96480332</v>
       </c>
       <c r="Q55">
-        <v>185.41087082</v>
+        <v>183.76480332</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1941446318648261</v>
+        <v>0.1968288391311596</v>
       </c>
       <c r="T55">
-        <v>1.034324423997298</v>
+        <v>1.053039904967109</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.527588035927822</v>
+        <v>3.311024663409574</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1147710660003334</v>
+        <v>0.1145130550241986</v>
       </c>
       <c r="C56">
-        <v>914.6040465283162</v>
+        <v>908.4928988433707</v>
       </c>
       <c r="D56">
-        <v>1319.568046528316</v>
+        <v>1324.522898843371</v>
       </c>
       <c r="E56">
-        <v>-323.736</v>
+        <v>-312.67</v>
       </c>
       <c r="F56">
-        <v>597.564</v>
+        <v>608.63</v>
       </c>
       <c r="G56">
         <v>192.6</v>
@@ -5879,28 +5879,28 @@
         <v>126.825</v>
       </c>
       <c r="M56">
-        <v>38.3038524</v>
+        <v>39.01318300000001</v>
       </c>
       <c r="N56">
-        <v>88.52114760000001</v>
+        <v>87.81181699999999</v>
       </c>
       <c r="O56">
-        <v>26.55634428</v>
+        <v>26.3435451</v>
       </c>
       <c r="P56">
-        <v>61.96480332</v>
+        <v>61.46827189999999</v>
       </c>
       <c r="Q56">
-        <v>183.76480332</v>
+        <v>183.2682719</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1968288391311596</v>
+        <v>0.1996323444982191</v>
       </c>
       <c r="T56">
-        <v>1.053039904967109</v>
+        <v>1.072587185091133</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.311024663409574</v>
+        <v>3.250824214983945</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1145130550241986</v>
+        <v>0.1142550440480637</v>
       </c>
       <c r="C57">
-        <v>908.4928988433707</v>
+        <v>902.4191014019374</v>
       </c>
       <c r="D57">
-        <v>1324.522898843371</v>
+        <v>1329.515101401937</v>
       </c>
       <c r="E57">
-        <v>-312.67</v>
+        <v>-301.6039999999999</v>
       </c>
       <c r="F57">
-        <v>608.63</v>
+        <v>619.696</v>
       </c>
       <c r="G57">
         <v>192.6</v>
@@ -5961,28 +5961,28 @@
         <v>126.825</v>
       </c>
       <c r="M57">
-        <v>39.01318300000001</v>
+        <v>39.72251360000001</v>
       </c>
       <c r="N57">
-        <v>87.81181699999999</v>
+        <v>87.1024864</v>
       </c>
       <c r="O57">
-        <v>26.3435451</v>
+        <v>26.13074592</v>
       </c>
       <c r="P57">
-        <v>61.46827189999999</v>
+        <v>60.97174048000001</v>
       </c>
       <c r="Q57">
-        <v>183.2682719</v>
+        <v>182.77174048</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1996323444982191</v>
+        <v>0.2025632819274176</v>
       </c>
       <c r="T57">
-        <v>1.072587185091133</v>
+        <v>1.093022977948068</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.250824214983945</v>
+        <v>3.192773782573517</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1142550440480637</v>
+        <v>0.1139970330719289</v>
       </c>
       <c r="C58">
-        <v>902.4191014019374</v>
+        <v>896.3830781274195</v>
       </c>
       <c r="D58">
-        <v>1329.515101401937</v>
+        <v>1334.54507812742</v>
       </c>
       <c r="E58">
-        <v>-301.6039999999999</v>
+        <v>-290.5379999999999</v>
       </c>
       <c r="F58">
-        <v>619.696</v>
+        <v>630.7620000000001</v>
       </c>
       <c r="G58">
         <v>192.6</v>
@@ -6043,28 +6043,28 @@
         <v>126.825</v>
       </c>
       <c r="M58">
-        <v>39.72251360000001</v>
+        <v>40.43184420000001</v>
       </c>
       <c r="N58">
-        <v>87.1024864</v>
+        <v>86.39315579999999</v>
       </c>
       <c r="O58">
-        <v>26.13074592</v>
+        <v>25.91794673999999</v>
       </c>
       <c r="P58">
-        <v>60.97174048000001</v>
+        <v>60.47520906</v>
       </c>
       <c r="Q58">
-        <v>182.77174048</v>
+        <v>182.27520906</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2025632819274176</v>
+        <v>0.2056305420277416</v>
       </c>
       <c r="T58">
-        <v>1.093022977948068</v>
+        <v>1.114409272798349</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.192773782573517</v>
+        <v>3.136760207440648</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1139970330719289</v>
+        <v>0.113739022095794</v>
       </c>
       <c r="C59">
-        <v>896.3830781274195</v>
+        <v>890.3852593829301</v>
       </c>
       <c r="D59">
-        <v>1334.54507812742</v>
+        <v>1339.61325938293</v>
       </c>
       <c r="E59">
-        <v>-290.5379999999999</v>
+        <v>-279.472</v>
       </c>
       <c r="F59">
-        <v>630.7620000000001</v>
+        <v>641.828</v>
       </c>
       <c r="G59">
         <v>192.6</v>
@@ -6125,28 +6125,28 @@
         <v>126.825</v>
       </c>
       <c r="M59">
-        <v>40.43184420000001</v>
+        <v>41.1411748</v>
       </c>
       <c r="N59">
-        <v>86.39315579999999</v>
+        <v>85.6838252</v>
       </c>
       <c r="O59">
-        <v>25.91794673999999</v>
+        <v>25.70514756</v>
       </c>
       <c r="P59">
-        <v>60.47520906</v>
+        <v>59.97867764</v>
       </c>
       <c r="Q59">
-        <v>182.27520906</v>
+        <v>181.77867764</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2056305420277416</v>
+        <v>0.208843862132843</v>
       </c>
       <c r="T59">
-        <v>1.114409272798349</v>
+        <v>1.136813962641501</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.136760207440648</v>
+        <v>3.082678134898569</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.113739022095794</v>
+        <v>0.1134810111196592</v>
       </c>
       <c r="C60">
-        <v>890.3852593829298</v>
+        <v>884.4260820940373</v>
       </c>
       <c r="D60">
-        <v>1339.61325938293</v>
+        <v>1344.720082094037</v>
       </c>
       <c r="E60">
-        <v>-279.4720000000001</v>
+        <v>-268.4060000000001</v>
       </c>
       <c r="F60">
-        <v>641.8279999999999</v>
+        <v>652.8939999999999</v>
       </c>
       <c r="G60">
         <v>192.6</v>
@@ -6207,28 +6207,28 @@
         <v>126.825</v>
       </c>
       <c r="M60">
-        <v>41.14117479999999</v>
+        <v>41.8505054</v>
       </c>
       <c r="N60">
-        <v>85.6838252</v>
+        <v>84.97449460000001</v>
       </c>
       <c r="O60">
-        <v>25.70514756</v>
+        <v>25.49234838</v>
       </c>
       <c r="P60">
-        <v>59.97867764</v>
+        <v>59.48214622000001</v>
       </c>
       <c r="Q60">
-        <v>181.77867764</v>
+        <v>181.28214622</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.208843862132843</v>
+        <v>0.2122139295601444</v>
       </c>
       <c r="T60">
-        <v>1.136813962641501</v>
+        <v>1.160311564184318</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.082678134898569</v>
+        <v>3.030429352951136</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1134810111196592</v>
+        <v>0.1164990001435244</v>
       </c>
       <c r="C61">
-        <v>884.4260820940373</v>
+        <v>815.9568594219755</v>
       </c>
       <c r="D61">
-        <v>1344.720082094037</v>
+        <v>1287.316859421976</v>
       </c>
       <c r="E61">
-        <v>-268.4060000000001</v>
+        <v>-257.34</v>
       </c>
       <c r="F61">
-        <v>652.8939999999999</v>
+        <v>663.9599999999999</v>
       </c>
       <c r="G61">
         <v>192.6</v>
@@ -6289,45 +6289,45 @@
         <v>126.825</v>
       </c>
       <c r="M61">
-        <v>41.8505054</v>
+        <v>47.738724</v>
       </c>
       <c r="N61">
-        <v>84.97449460000001</v>
+        <v>79.086276</v>
       </c>
       <c r="O61">
-        <v>25.49234838</v>
+        <v>23.7258828</v>
       </c>
       <c r="P61">
-        <v>59.48214622000001</v>
+        <v>55.3603932</v>
       </c>
       <c r="Q61">
-        <v>181.28214622</v>
+        <v>177.1603932</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2122139295601444</v>
+        <v>0.2157525003588109</v>
       </c>
       <c r="T61">
-        <v>1.160311564184318</v>
+        <v>1.184984045804276</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.030429352951136</v>
+        <v>2.656648300863676</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1164990001435244</v>
+        <v>0.1162955891673895</v>
       </c>
       <c r="C62">
-        <v>815.9568594219755</v>
+        <v>808.6053383285652</v>
       </c>
       <c r="D62">
-        <v>1287.316859421976</v>
+        <v>1291.031338328565</v>
       </c>
       <c r="E62">
-        <v>-257.34</v>
+        <v>-246.274</v>
       </c>
       <c r="F62">
-        <v>663.9599999999999</v>
+        <v>675.026</v>
       </c>
       <c r="G62">
         <v>192.6</v>
@@ -6371,28 +6371,28 @@
         <v>126.825</v>
       </c>
       <c r="M62">
-        <v>47.738724</v>
+        <v>48.5343694</v>
       </c>
       <c r="N62">
-        <v>79.086276</v>
+        <v>78.2906306</v>
       </c>
       <c r="O62">
-        <v>23.7258828</v>
+        <v>23.48718918</v>
       </c>
       <c r="P62">
-        <v>55.3603932</v>
+        <v>54.80344142</v>
       </c>
       <c r="Q62">
-        <v>177.1603932</v>
+        <v>176.60344142</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2157525003588109</v>
+        <v>0.2194725363266397</v>
       </c>
       <c r="T62">
-        <v>1.184984045804276</v>
+        <v>1.210921782891924</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.656648300863676</v>
+        <v>2.613096689374108</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1162955891673895</v>
+        <v>0.1160921781912547</v>
       </c>
       <c r="C63">
-        <v>808.6053383285652</v>
+        <v>801.2753150973539</v>
       </c>
       <c r="D63">
-        <v>1291.031338328565</v>
+        <v>1294.767315097354</v>
       </c>
       <c r="E63">
-        <v>-246.274</v>
+        <v>-235.208</v>
       </c>
       <c r="F63">
-        <v>675.026</v>
+        <v>686.092</v>
       </c>
       <c r="G63">
         <v>192.6</v>
@@ -6453,28 +6453,28 @@
         <v>126.825</v>
       </c>
       <c r="M63">
-        <v>48.5343694</v>
+        <v>49.3300148</v>
       </c>
       <c r="N63">
-        <v>78.2906306</v>
+        <v>77.4949852</v>
       </c>
       <c r="O63">
-        <v>23.48718918</v>
+        <v>23.24849556</v>
       </c>
       <c r="P63">
-        <v>54.80344142</v>
+        <v>54.24648964000001</v>
       </c>
       <c r="Q63">
-        <v>176.60344142</v>
+        <v>176.04648964</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2194725363266397</v>
+        <v>0.2233883636611965</v>
       </c>
       <c r="T63">
-        <v>1.210921782891924</v>
+        <v>1.238224664036817</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.613096689374108</v>
+        <v>2.570949968577751</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1160921781912547</v>
+        <v>0.1158887672151198</v>
       </c>
       <c r="C64">
-        <v>801.2753150973539</v>
+        <v>793.9669769010361</v>
       </c>
       <c r="D64">
-        <v>1294.767315097354</v>
+        <v>1298.524976901036</v>
       </c>
       <c r="E64">
-        <v>-235.208</v>
+        <v>-224.1420000000001</v>
       </c>
       <c r="F64">
-        <v>686.092</v>
+        <v>697.1579999999999</v>
       </c>
       <c r="G64">
         <v>192.6</v>
@@ -6535,28 +6535,28 @@
         <v>126.825</v>
       </c>
       <c r="M64">
-        <v>49.3300148</v>
+        <v>50.1256602</v>
       </c>
       <c r="N64">
-        <v>77.4949852</v>
+        <v>76.6993398</v>
       </c>
       <c r="O64">
-        <v>23.24849556</v>
+        <v>23.00980194</v>
       </c>
       <c r="P64">
-        <v>54.24648964000001</v>
+        <v>53.68953786</v>
       </c>
       <c r="Q64">
-        <v>176.04648964</v>
+        <v>175.48953786</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2233883636611965</v>
+        <v>0.2275158573381617</v>
       </c>
       <c r="T64">
-        <v>1.238224664036817</v>
+        <v>1.267003376594948</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.570949968577751</v>
+        <v>2.530141238917787</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1158887672151198</v>
+        <v>0.117432556238985</v>
       </c>
       <c r="C65">
-        <v>793.9669769010361</v>
+        <v>754.9158160774221</v>
       </c>
       <c r="D65">
-        <v>1298.524976901036</v>
+        <v>1270.539816077422</v>
       </c>
       <c r="E65">
-        <v>-224.1420000000001</v>
+        <v>-213.076</v>
       </c>
       <c r="F65">
-        <v>697.1579999999999</v>
+        <v>708.2239999999999</v>
       </c>
       <c r="G65">
         <v>192.6</v>
@@ -6617,45 +6617,45 @@
         <v>126.825</v>
       </c>
       <c r="M65">
-        <v>50.1256602</v>
+        <v>53.6833792</v>
       </c>
       <c r="N65">
-        <v>76.6993398</v>
+        <v>73.1416208</v>
       </c>
       <c r="O65">
-        <v>23.00980194</v>
+        <v>21.94248624</v>
       </c>
       <c r="P65">
-        <v>53.68953786</v>
+        <v>51.19913456</v>
       </c>
       <c r="Q65">
-        <v>175.48953786</v>
+        <v>172.99913456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2275158573381617</v>
+        <v>0.2318726562194027</v>
       </c>
       <c r="T65">
-        <v>1.267003376594948</v>
+        <v>1.297380906517419</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.530141238917787</v>
+        <v>2.362463054486704</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.117432556238985</v>
+        <v>0.1172564452628501</v>
       </c>
       <c r="C66">
-        <v>754.9158160774221</v>
+        <v>746.981178215638</v>
       </c>
       <c r="D66">
-        <v>1270.539816077422</v>
+        <v>1273.671178215638</v>
       </c>
       <c r="E66">
-        <v>-213.076</v>
+        <v>-202.01</v>
       </c>
       <c r="F66">
-        <v>708.2239999999999</v>
+        <v>719.29</v>
       </c>
       <c r="G66">
         <v>192.6</v>
@@ -6699,28 +6699,28 @@
         <v>126.825</v>
       </c>
       <c r="M66">
-        <v>53.6833792</v>
+        <v>54.522182</v>
       </c>
       <c r="N66">
-        <v>73.1416208</v>
+        <v>72.302818</v>
       </c>
       <c r="O66">
-        <v>21.94248624</v>
+        <v>21.6908454</v>
       </c>
       <c r="P66">
-        <v>51.19913456</v>
+        <v>50.6119726</v>
       </c>
       <c r="Q66">
-        <v>172.99913456</v>
+        <v>172.4119726</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2318726562194027</v>
+        <v>0.2364784150367146</v>
       </c>
       <c r="T66">
-        <v>1.297380906517419</v>
+        <v>1.329494295292602</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.362463054486704</v>
+        <v>2.326117469033063</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1172564452628501</v>
+        <v>0.1170803342867153</v>
       </c>
       <c r="C67">
-        <v>746.981178215638</v>
+        <v>739.0620135484821</v>
       </c>
       <c r="D67">
-        <v>1273.671178215638</v>
+        <v>1276.818013548482</v>
       </c>
       <c r="E67">
-        <v>-202.01</v>
+        <v>-190.944</v>
       </c>
       <c r="F67">
-        <v>719.29</v>
+        <v>730.356</v>
       </c>
       <c r="G67">
         <v>192.6</v>
@@ -6781,28 +6781,28 @@
         <v>126.825</v>
       </c>
       <c r="M67">
-        <v>54.522182</v>
+        <v>55.3609848</v>
       </c>
       <c r="N67">
-        <v>72.302818</v>
+        <v>71.46401520000001</v>
       </c>
       <c r="O67">
-        <v>21.6908454</v>
+        <v>21.43920456</v>
       </c>
       <c r="P67">
-        <v>50.6119726</v>
+        <v>50.02481064000001</v>
       </c>
       <c r="Q67">
-        <v>172.4119726</v>
+        <v>171.82481064</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2364784150367146</v>
+        <v>0.2413551008432802</v>
       </c>
       <c r="T67">
-        <v>1.329494295292602</v>
+        <v>1.363496706936915</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.326117469033063</v>
+        <v>2.290873264956804</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1170803342867153</v>
+        <v>0.1169042233105804</v>
       </c>
       <c r="C68">
-        <v>739.0620135484821</v>
+        <v>731.158437048003</v>
       </c>
       <c r="D68">
-        <v>1276.818013548482</v>
+        <v>1279.980437048003</v>
       </c>
       <c r="E68">
-        <v>-190.944</v>
+        <v>-179.8779999999999</v>
       </c>
       <c r="F68">
-        <v>730.356</v>
+        <v>741.422</v>
       </c>
       <c r="G68">
         <v>192.6</v>
@@ -6863,28 +6863,28 @@
         <v>126.825</v>
       </c>
       <c r="M68">
-        <v>55.3609848</v>
+        <v>56.19978760000001</v>
       </c>
       <c r="N68">
-        <v>71.46401520000001</v>
+        <v>70.6252124</v>
       </c>
       <c r="O68">
-        <v>21.43920456</v>
+        <v>21.18756372</v>
       </c>
       <c r="P68">
-        <v>50.02481064000001</v>
+        <v>49.43764868</v>
       </c>
       <c r="Q68">
-        <v>171.82481064</v>
+        <v>171.23764868</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2413551008432802</v>
+        <v>0.2465273433653953</v>
       </c>
       <c r="T68">
-        <v>1.363496706936915</v>
+        <v>1.399559870802094</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.290873264956804</v>
+        <v>2.256681126673866</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1169042233105804</v>
+        <v>0.1167281123344456</v>
       </c>
       <c r="C69">
-        <v>731.158437048003</v>
+        <v>723.2705648281297</v>
       </c>
       <c r="D69">
-        <v>1279.980437048003</v>
+        <v>1283.15856482813</v>
       </c>
       <c r="E69">
-        <v>-179.8779999999999</v>
+        <v>-168.812</v>
       </c>
       <c r="F69">
-        <v>741.422</v>
+        <v>752.4879999999999</v>
       </c>
       <c r="G69">
         <v>192.6</v>
@@ -6945,28 +6945,28 @@
         <v>126.825</v>
       </c>
       <c r="M69">
-        <v>56.19978760000001</v>
+        <v>57.0385904</v>
       </c>
       <c r="N69">
-        <v>70.6252124</v>
+        <v>69.7864096</v>
       </c>
       <c r="O69">
-        <v>21.18756372</v>
+        <v>20.93592288</v>
       </c>
       <c r="P69">
-        <v>49.43764868</v>
+        <v>48.85048672</v>
       </c>
       <c r="Q69">
-        <v>171.23764868</v>
+        <v>170.65048672</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2465273433653953</v>
+        <v>0.2520228510451425</v>
       </c>
       <c r="T69">
-        <v>1.399559870802094</v>
+        <v>1.437876982408847</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.256681126673866</v>
+        <v>2.223494639516898</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1167281123344456</v>
+        <v>0.1165520013583107</v>
       </c>
       <c r="C70">
-        <v>723.2705648281297</v>
+        <v>715.3985141588806</v>
       </c>
       <c r="D70">
-        <v>1283.15856482813</v>
+        <v>1286.352514158881</v>
       </c>
       <c r="E70">
-        <v>-168.812</v>
+        <v>-157.746</v>
       </c>
       <c r="F70">
-        <v>752.4879999999999</v>
+        <v>763.554</v>
       </c>
       <c r="G70">
         <v>192.6</v>
@@ -7027,28 +7027,28 @@
         <v>126.825</v>
       </c>
       <c r="M70">
-        <v>57.0385904</v>
+        <v>57.8773932</v>
       </c>
       <c r="N70">
-        <v>69.7864096</v>
+        <v>68.9476068</v>
       </c>
       <c r="O70">
-        <v>20.93592288</v>
+        <v>20.68428204</v>
       </c>
       <c r="P70">
-        <v>48.85048672</v>
+        <v>48.26332476</v>
       </c>
       <c r="Q70">
-        <v>170.65048672</v>
+        <v>170.06332476</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2520228510451425</v>
+        <v>0.2578729076074541</v>
       </c>
       <c r="T70">
-        <v>1.437876982408847</v>
+        <v>1.478666165732166</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.223494639516898</v>
+        <v>2.1912700795239</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1165520013583107</v>
+        <v>0.1163758903821759</v>
       </c>
       <c r="C71">
-        <v>715.3985141588806</v>
+        <v>707.5424034807903</v>
       </c>
       <c r="D71">
-        <v>1286.352514158881</v>
+        <v>1289.56240348079</v>
       </c>
       <c r="E71">
-        <v>-157.746</v>
+        <v>-146.6799999999999</v>
       </c>
       <c r="F71">
-        <v>763.554</v>
+        <v>774.62</v>
       </c>
       <c r="G71">
         <v>192.6</v>
@@ -7109,28 +7109,28 @@
         <v>126.825</v>
       </c>
       <c r="M71">
-        <v>57.8773932</v>
+        <v>58.716196</v>
       </c>
       <c r="N71">
-        <v>68.9476068</v>
+        <v>68.10880399999999</v>
       </c>
       <c r="O71">
-        <v>20.68428204</v>
+        <v>20.4326412</v>
       </c>
       <c r="P71">
-        <v>48.26332476</v>
+        <v>47.6761628</v>
       </c>
       <c r="Q71">
-        <v>170.06332476</v>
+        <v>169.4761628</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2578729076074541</v>
+        <v>0.2641129679405864</v>
       </c>
       <c r="T71">
-        <v>1.478666165732166</v>
+        <v>1.522174627943705</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.1912700795239</v>
+        <v>2.159966221244987</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1163758903821759</v>
+        <v>0.1161997794060411</v>
       </c>
       <c r="C72">
-        <v>707.5424034807903</v>
+        <v>699.7023524195494</v>
       </c>
       <c r="D72">
-        <v>1289.56240348079</v>
+        <v>1292.788352419549</v>
       </c>
       <c r="E72">
-        <v>-146.6799999999999</v>
+        <v>-135.6139999999999</v>
       </c>
       <c r="F72">
-        <v>774.62</v>
+        <v>785.686</v>
       </c>
       <c r="G72">
         <v>192.6</v>
@@ -7191,28 +7191,28 @@
         <v>126.825</v>
       </c>
       <c r="M72">
-        <v>58.716196</v>
+        <v>59.55499880000001</v>
       </c>
       <c r="N72">
-        <v>68.10880399999999</v>
+        <v>67.2700012</v>
       </c>
       <c r="O72">
-        <v>20.4326412</v>
+        <v>20.18100036</v>
       </c>
       <c r="P72">
-        <v>47.6761628</v>
+        <v>47.08900084</v>
       </c>
       <c r="Q72">
-        <v>169.4761628</v>
+        <v>168.88900084</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2641129679405864</v>
+        <v>0.2707833772622106</v>
       </c>
       <c r="T72">
-        <v>1.522174627943705</v>
+        <v>1.56868367375604</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.159966221244987</v>
+        <v>2.129544161790832</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1161997794060411</v>
+        <v>0.1160236684299062</v>
       </c>
       <c r="C73">
-        <v>699.7023524195495</v>
+        <v>691.8784818008651</v>
       </c>
       <c r="D73">
-        <v>1292.788352419549</v>
+        <v>1296.030481800865</v>
       </c>
       <c r="E73">
-        <v>-135.614</v>
+        <v>-124.548</v>
       </c>
       <c r="F73">
-        <v>785.6859999999999</v>
+        <v>796.752</v>
       </c>
       <c r="G73">
         <v>192.6</v>
@@ -7273,28 +7273,28 @@
         <v>126.825</v>
       </c>
       <c r="M73">
-        <v>59.5549988</v>
+        <v>60.3938016</v>
       </c>
       <c r="N73">
-        <v>67.2700012</v>
+        <v>66.4311984</v>
       </c>
       <c r="O73">
-        <v>20.18100036</v>
+        <v>19.92935952</v>
       </c>
       <c r="P73">
-        <v>47.08900084</v>
+        <v>46.50183888</v>
       </c>
       <c r="Q73">
-        <v>168.88900084</v>
+        <v>168.30183888</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2707833772622105</v>
+        <v>0.2779302443925222</v>
       </c>
       <c r="T73">
-        <v>1.568683673756039</v>
+        <v>1.618514794269255</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.129544161790832</v>
+        <v>2.099967159543737</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1160236684299062</v>
+        <v>0.1158475574537714</v>
       </c>
       <c r="C74">
-        <v>691.8784818008651</v>
+        <v>684.0709136655465</v>
       </c>
       <c r="D74">
-        <v>1296.030481800865</v>
+        <v>1299.288913665546</v>
       </c>
       <c r="E74">
-        <v>-124.548</v>
+        <v>-113.4820000000001</v>
       </c>
       <c r="F74">
-        <v>796.752</v>
+        <v>807.8179999999999</v>
       </c>
       <c r="G74">
         <v>192.6</v>
@@ -7355,28 +7355,28 @@
         <v>126.825</v>
       </c>
       <c r="M74">
-        <v>60.3938016</v>
+        <v>61.23260439999999</v>
       </c>
       <c r="N74">
-        <v>66.4311984</v>
+        <v>65.5923956</v>
       </c>
       <c r="O74">
-        <v>19.92935952</v>
+        <v>19.67771868</v>
       </c>
       <c r="P74">
-        <v>46.50183888</v>
+        <v>45.91467692000001</v>
       </c>
       <c r="Q74">
-        <v>168.30183888</v>
+        <v>167.71467692</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2779302443925222</v>
+        <v>0.2856065090880421</v>
       </c>
       <c r="T74">
-        <v>1.618514794269255</v>
+        <v>1.672037108894561</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.099967159543737</v>
+        <v>2.07120048612533</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1158475574537714</v>
+        <v>0.1156714464776365</v>
       </c>
       <c r="C75">
-        <v>684.0709136655465</v>
+        <v>676.2797712848181</v>
       </c>
       <c r="D75">
-        <v>1299.288913665546</v>
+        <v>1302.563771284818</v>
       </c>
       <c r="E75">
-        <v>-113.4820000000001</v>
+        <v>-102.4160000000001</v>
       </c>
       <c r="F75">
-        <v>807.8179999999999</v>
+        <v>818.8839999999999</v>
       </c>
       <c r="G75">
         <v>192.6</v>
@@ -7437,28 +7437,28 @@
         <v>126.825</v>
       </c>
       <c r="M75">
-        <v>61.23260439999999</v>
+        <v>62.0714072</v>
       </c>
       <c r="N75">
-        <v>65.5923956</v>
+        <v>64.75359280000001</v>
       </c>
       <c r="O75">
-        <v>19.67771868</v>
+        <v>19.42607784</v>
       </c>
       <c r="P75">
-        <v>45.91467692000001</v>
+        <v>45.32751496</v>
       </c>
       <c r="Q75">
-        <v>167.71467692</v>
+        <v>167.12751496</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2856065090880421</v>
+        <v>0.2938732556832174</v>
       </c>
       <c r="T75">
-        <v>1.672037108894561</v>
+        <v>1.729676524644891</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.07120048612533</v>
+        <v>2.043211290366879</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1156714464776365</v>
+        <v>0.1154953355015017</v>
       </c>
       <c r="C76">
-        <v>676.2797712848181</v>
+        <v>668.5051791758659</v>
       </c>
       <c r="D76">
-        <v>1302.563771284818</v>
+        <v>1305.855179175866</v>
       </c>
       <c r="E76">
-        <v>-102.4160000000001</v>
+        <v>-91.35000000000002</v>
       </c>
       <c r="F76">
-        <v>818.8839999999999</v>
+        <v>829.9499999999999</v>
       </c>
       <c r="G76">
         <v>192.6</v>
@@ -7519,28 +7519,28 @@
         <v>126.825</v>
       </c>
       <c r="M76">
-        <v>62.0714072</v>
+        <v>62.91021</v>
       </c>
       <c r="N76">
-        <v>64.75359280000001</v>
+        <v>63.91479</v>
       </c>
       <c r="O76">
-        <v>19.42607784</v>
+        <v>19.174437</v>
       </c>
       <c r="P76">
-        <v>45.32751496</v>
+        <v>44.740353</v>
       </c>
       <c r="Q76">
-        <v>167.12751496</v>
+        <v>166.540353</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2938732556832174</v>
+        <v>0.3028013420060067</v>
       </c>
       <c r="T76">
-        <v>1.729676524644891</v>
+        <v>1.791927093655247</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.043211290366879</v>
+        <v>2.015968473161988</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1154953355015017</v>
+        <v>0.1228736245253668</v>
       </c>
       <c r="C77">
-        <v>668.5051791758659</v>
+        <v>532.4291385218202</v>
       </c>
       <c r="D77">
-        <v>1305.855179175866</v>
+        <v>1180.84513852182</v>
       </c>
       <c r="E77">
-        <v>-91.35000000000002</v>
+        <v>-80.28399999999999</v>
       </c>
       <c r="F77">
-        <v>829.9499999999999</v>
+        <v>841.016</v>
       </c>
       <c r="G77">
         <v>192.6</v>
@@ -7601,45 +7601,45 @@
         <v>126.825</v>
       </c>
       <c r="M77">
-        <v>62.91021</v>
+        <v>75.69144</v>
       </c>
       <c r="N77">
-        <v>63.91479</v>
+        <v>51.13356</v>
       </c>
       <c r="O77">
-        <v>19.174437</v>
+        <v>15.340068</v>
       </c>
       <c r="P77">
-        <v>44.740353</v>
+        <v>35.793492</v>
       </c>
       <c r="Q77">
-        <v>166.540353</v>
+        <v>157.593492</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3028013420060067</v>
+        <v>0.3124734355223618</v>
       </c>
       <c r="T77">
-        <v>1.791927093655247</v>
+        <v>1.859365210083133</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.3</v>
       </c>
       <c r="W77">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.015968473161988</v>
+        <v>1.675552744141213</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1228736245253668</v>
+        <v>0.122796913549232</v>
       </c>
       <c r="C78">
-        <v>532.4291385218202</v>
+        <v>522.5395984481282</v>
       </c>
       <c r="D78">
-        <v>1180.84513852182</v>
+        <v>1182.021598448128</v>
       </c>
       <c r="E78">
-        <v>-80.28399999999999</v>
+        <v>-69.21799999999996</v>
       </c>
       <c r="F78">
-        <v>841.016</v>
+        <v>852.082</v>
       </c>
       <c r="G78">
         <v>192.6</v>
@@ -7683,28 +7683,28 @@
         <v>126.825</v>
       </c>
       <c r="M78">
-        <v>75.69144</v>
+        <v>76.68737999999999</v>
       </c>
       <c r="N78">
-        <v>51.13356</v>
+        <v>50.13762000000001</v>
       </c>
       <c r="O78">
-        <v>15.340068</v>
+        <v>15.041286</v>
       </c>
       <c r="P78">
-        <v>35.793492</v>
+        <v>35.09633400000001</v>
       </c>
       <c r="Q78">
-        <v>157.593492</v>
+        <v>156.896334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3124734355223618</v>
+        <v>0.3229865806488347</v>
       </c>
       <c r="T78">
-        <v>1.859365210083133</v>
+        <v>1.932667510548226</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.675552744141213</v>
+        <v>1.653792318892626</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.122796913549232</v>
+        <v>0.1227202025730972</v>
       </c>
       <c r="C79">
-        <v>522.5395984481282</v>
+        <v>512.6524048942406</v>
       </c>
       <c r="D79">
-        <v>1182.021598448128</v>
+        <v>1183.200404894241</v>
       </c>
       <c r="E79">
-        <v>-69.21799999999996</v>
+        <v>-58.15200000000004</v>
       </c>
       <c r="F79">
-        <v>852.082</v>
+        <v>863.1479999999999</v>
       </c>
       <c r="G79">
         <v>192.6</v>
@@ -7765,28 +7765,28 @@
         <v>126.825</v>
       </c>
       <c r="M79">
-        <v>76.68737999999999</v>
+        <v>77.68331999999999</v>
       </c>
       <c r="N79">
-        <v>50.13762000000001</v>
+        <v>49.14168000000001</v>
       </c>
       <c r="O79">
-        <v>15.041286</v>
+        <v>14.742504</v>
       </c>
       <c r="P79">
-        <v>35.09633400000001</v>
+        <v>34.399176</v>
       </c>
       <c r="Q79">
-        <v>156.896334</v>
+        <v>156.199176</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3229865806488347</v>
+        <v>0.3344554662413507</v>
       </c>
       <c r="T79">
-        <v>1.932667510548226</v>
+        <v>2.012633656510145</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.653792318892626</v>
+        <v>1.632589853265798</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1227202025730972</v>
+        <v>0.1226434915969623</v>
       </c>
       <c r="C80">
-        <v>512.6524048942406</v>
+        <v>502.7675648875766</v>
       </c>
       <c r="D80">
-        <v>1183.200404894241</v>
+        <v>1184.381564887577</v>
       </c>
       <c r="E80">
-        <v>-58.15200000000004</v>
+        <v>-47.08600000000001</v>
       </c>
       <c r="F80">
-        <v>863.1479999999999</v>
+        <v>874.2139999999999</v>
       </c>
       <c r="G80">
         <v>192.6</v>
@@ -7847,28 +7847,28 @@
         <v>126.825</v>
       </c>
       <c r="M80">
-        <v>77.68331999999999</v>
+        <v>78.67925999999999</v>
       </c>
       <c r="N80">
-        <v>49.14168000000001</v>
+        <v>48.14574000000002</v>
       </c>
       <c r="O80">
-        <v>14.742504</v>
+        <v>14.443722</v>
       </c>
       <c r="P80">
-        <v>34.399176</v>
+        <v>33.70201800000001</v>
       </c>
       <c r="Q80">
-        <v>156.199176</v>
+        <v>155.502018</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3344554662413507</v>
+        <v>0.3470166266522015</v>
       </c>
       <c r="T80">
-        <v>2.012633656510145</v>
+        <v>2.10021562589701</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.632589853265798</v>
+        <v>1.611924158920661</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1226434915969623</v>
+        <v>0.1225667806208274</v>
       </c>
       <c r="C81">
-        <v>502.7675648875766</v>
+        <v>492.885085483646</v>
       </c>
       <c r="D81">
-        <v>1184.381564887577</v>
+        <v>1185.565085483646</v>
       </c>
       <c r="E81">
-        <v>-47.08600000000001</v>
+        <v>-36.01999999999998</v>
       </c>
       <c r="F81">
-        <v>874.2139999999999</v>
+        <v>885.28</v>
       </c>
       <c r="G81">
         <v>192.6</v>
@@ -7929,28 +7929,28 @@
         <v>126.825</v>
       </c>
       <c r="M81">
-        <v>78.67925999999999</v>
+        <v>79.67519999999999</v>
       </c>
       <c r="N81">
-        <v>48.14574000000002</v>
+        <v>47.14980000000001</v>
       </c>
       <c r="O81">
-        <v>14.443722</v>
+        <v>14.14494</v>
       </c>
       <c r="P81">
-        <v>33.70201800000001</v>
+        <v>33.00486000000001</v>
       </c>
       <c r="Q81">
-        <v>155.502018</v>
+        <v>154.80486</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3470166266522015</v>
+        <v>0.3608339031041373</v>
       </c>
       <c r="T81">
-        <v>2.10021562589701</v>
+        <v>2.196555792222561</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.611924158920661</v>
+        <v>1.591775106934153</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1225667806208274</v>
+        <v>0.1224900696446926</v>
       </c>
       <c r="C82">
-        <v>492.885085483646</v>
+        <v>483.0049737661859</v>
       </c>
       <c r="D82">
-        <v>1185.565085483646</v>
+        <v>1186.750973766186</v>
       </c>
       <c r="E82">
-        <v>-36.01999999999998</v>
+        <v>-24.95399999999995</v>
       </c>
       <c r="F82">
-        <v>885.28</v>
+        <v>896.346</v>
       </c>
       <c r="G82">
         <v>192.6</v>
@@ -8011,28 +8011,28 @@
         <v>126.825</v>
       </c>
       <c r="M82">
-        <v>79.67519999999999</v>
+        <v>80.67113999999999</v>
       </c>
       <c r="N82">
-        <v>47.14980000000001</v>
+        <v>46.15386000000001</v>
       </c>
       <c r="O82">
-        <v>14.14494</v>
+        <v>13.846158</v>
       </c>
       <c r="P82">
-        <v>33.00486000000001</v>
+        <v>32.30770200000001</v>
       </c>
       <c r="Q82">
-        <v>154.80486</v>
+        <v>154.107702</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3608339031041373</v>
+        <v>0.3761056297089085</v>
       </c>
       <c r="T82">
-        <v>2.196555792222561</v>
+        <v>2.303037028687644</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.591775106934153</v>
+        <v>1.572123562404101</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1224900696446926</v>
+        <v>0.1224133586685578</v>
       </c>
       <c r="C83">
-        <v>483.0049737661859</v>
+        <v>473.1272368473074</v>
       </c>
       <c r="D83">
-        <v>1186.750973766186</v>
+        <v>1187.939236847307</v>
       </c>
       <c r="E83">
-        <v>-24.95399999999995</v>
+        <v>-13.88799999999992</v>
       </c>
       <c r="F83">
-        <v>896.346</v>
+        <v>907.412</v>
       </c>
       <c r="G83">
         <v>192.6</v>
@@ -8093,28 +8093,28 @@
         <v>126.825</v>
       </c>
       <c r="M83">
-        <v>80.67113999999999</v>
+        <v>81.66708</v>
       </c>
       <c r="N83">
-        <v>46.15386000000001</v>
+        <v>45.15792</v>
       </c>
       <c r="O83">
-        <v>13.846158</v>
+        <v>13.547376</v>
       </c>
       <c r="P83">
-        <v>32.30770200000001</v>
+        <v>31.610544</v>
       </c>
       <c r="Q83">
-        <v>154.107702</v>
+        <v>153.410544</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3761056297089085</v>
+        <v>0.393074214825321</v>
       </c>
       <c r="T83">
-        <v>2.303037028687644</v>
+        <v>2.421349513648847</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.572123562404101</v>
+        <v>1.552951323838198</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1224133586685578</v>
+        <v>0.1223366476924229</v>
       </c>
       <c r="C84">
-        <v>473.1272368473074</v>
+        <v>463.2518818676339</v>
       </c>
       <c r="D84">
-        <v>1187.939236847307</v>
+        <v>1189.129881867634</v>
       </c>
       <c r="E84">
-        <v>-13.88799999999992</v>
+        <v>-2.822000000000003</v>
       </c>
       <c r="F84">
-        <v>907.412</v>
+        <v>918.478</v>
       </c>
       <c r="G84">
         <v>192.6</v>
@@ -8175,28 +8175,28 @@
         <v>126.825</v>
       </c>
       <c r="M84">
-        <v>81.66708</v>
+        <v>82.66301999999999</v>
       </c>
       <c r="N84">
-        <v>45.15792</v>
+        <v>44.16198000000001</v>
       </c>
       <c r="O84">
-        <v>13.547376</v>
+        <v>13.248594</v>
       </c>
       <c r="P84">
-        <v>31.610544</v>
+        <v>30.91338600000001</v>
       </c>
       <c r="Q84">
-        <v>153.410544</v>
+        <v>152.713386</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.393074214825321</v>
+        <v>0.4120391040730761</v>
       </c>
       <c r="T84">
-        <v>2.421349513648847</v>
+        <v>2.553581114487838</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.552951323838198</v>
+        <v>1.534241066924485</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1223366476924229</v>
+        <v>0.1222599367162881</v>
       </c>
       <c r="C85">
-        <v>463.2518818676339</v>
+        <v>453.3789159964432</v>
       </c>
       <c r="D85">
-        <v>1189.129881867634</v>
+        <v>1190.322915996443</v>
       </c>
       <c r="E85">
-        <v>-2.822000000000003</v>
+        <v>8.244000000000028</v>
       </c>
       <c r="F85">
-        <v>918.478</v>
+        <v>929.544</v>
       </c>
       <c r="G85">
         <v>192.6</v>
@@ -8257,28 +8257,28 @@
         <v>126.825</v>
       </c>
       <c r="M85">
-        <v>82.66301999999999</v>
+        <v>83.65895999999999</v>
       </c>
       <c r="N85">
-        <v>44.16198000000001</v>
+        <v>43.16604000000001</v>
       </c>
       <c r="O85">
-        <v>13.248594</v>
+        <v>12.949812</v>
       </c>
       <c r="P85">
-        <v>30.91338600000001</v>
+        <v>30.21622800000001</v>
       </c>
       <c r="Q85">
-        <v>152.713386</v>
+        <v>152.016228</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4120391040730761</v>
+        <v>0.4333746044768007</v>
       </c>
       <c r="T85">
-        <v>2.553581114487838</v>
+        <v>2.702341665431705</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.534241066924485</v>
+        <v>1.515976292318241</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1222599367162881</v>
+        <v>0.1607542729920572</v>
       </c>
       <c r="C86">
-        <v>453.3789159964435</v>
+        <v>43.71363462577926</v>
       </c>
       <c r="D86">
-        <v>1190.322915996443</v>
+        <v>791.7236346257791</v>
       </c>
       <c r="E86">
-        <v>8.243999999999915</v>
+        <v>19.30999999999995</v>
       </c>
       <c r="F86">
-        <v>929.5439999999999</v>
+        <v>940.6099999999999</v>
       </c>
       <c r="G86">
         <v>192.6</v>
@@ -8339,45 +8339,45 @@
         <v>126.825</v>
       </c>
       <c r="M86">
-        <v>83.65895999999998</v>
+        <v>138.081548</v>
       </c>
       <c r="N86">
-        <v>43.16604000000002</v>
+        <v>-11.256548</v>
       </c>
       <c r="O86">
-        <v>12.94981200000001</v>
+        <v>-3.376964399999999</v>
       </c>
       <c r="P86">
-        <v>30.21622800000002</v>
+        <v>-7.879583599999997</v>
       </c>
       <c r="Q86">
-        <v>152.016228</v>
+        <v>113.9204164</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4333746044768004</v>
+        <v>0.4690441020122325</v>
       </c>
       <c r="T86">
-        <v>2.702341665431702</v>
+        <v>2.951045187957729</v>
       </c>
       <c r="U86">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.3</v>
+        <v>0.2755436953820941</v>
       </c>
       <c r="W86">
-        <v>0.063</v>
+        <v>0.1063501855179086</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.515976292318241</v>
+        <v>0.9184789846069803</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1607542729920572</v>
+        <v>0.1617642729920572</v>
       </c>
       <c r="C87">
-        <v>43.71363462577926</v>
+        <v>25.7520550620045</v>
       </c>
       <c r="D87">
-        <v>791.7236346257791</v>
+        <v>784.8280550620044</v>
       </c>
       <c r="E87">
-        <v>19.30999999999995</v>
+        <v>30.37599999999998</v>
       </c>
       <c r="F87">
-        <v>940.6099999999999</v>
+        <v>951.6759999999999</v>
       </c>
       <c r="G87">
         <v>192.6</v>
@@ -8421,37 +8421,37 @@
         <v>126.825</v>
       </c>
       <c r="M87">
-        <v>138.081548</v>
+        <v>139.7060368</v>
       </c>
       <c r="N87">
-        <v>-11.256548</v>
+        <v>-12.88103679999999</v>
       </c>
       <c r="O87">
-        <v>-3.376964399999999</v>
+        <v>-3.864311039999997</v>
       </c>
       <c r="P87">
-        <v>-7.879583599999997</v>
+        <v>-9.016725759999993</v>
       </c>
       <c r="Q87">
-        <v>113.9204164</v>
+        <v>112.78327424</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4690441020122325</v>
+        <v>0.4992758235845348</v>
       </c>
       <c r="T87">
-        <v>2.951045187957729</v>
+        <v>3.161834129954709</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2755436953820941</v>
+        <v>0.2723396989241628</v>
       </c>
       <c r="W87">
-        <v>0.1063501855179086</v>
+        <v>0.1068205321979329</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9184789846069803</v>
+        <v>0.9077989964138758</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1617642729920572</v>
+        <v>0.1627742729920572</v>
       </c>
       <c r="C88">
-        <v>25.7520550620045</v>
+        <v>7.909553568668116</v>
       </c>
       <c r="D88">
-        <v>784.8280550620044</v>
+        <v>778.0515535686681</v>
       </c>
       <c r="E88">
-        <v>30.37599999999998</v>
+        <v>41.44200000000001</v>
       </c>
       <c r="F88">
-        <v>951.6759999999999</v>
+        <v>962.742</v>
       </c>
       <c r="G88">
         <v>192.6</v>
@@ -8503,37 +8503,37 @@
         <v>126.825</v>
       </c>
       <c r="M88">
-        <v>139.7060368</v>
+        <v>141.3305256</v>
       </c>
       <c r="N88">
-        <v>-12.88103679999999</v>
+        <v>-14.50552560000001</v>
       </c>
       <c r="O88">
-        <v>-3.864311039999997</v>
+        <v>-4.351657680000003</v>
       </c>
       <c r="P88">
-        <v>-9.016725759999993</v>
+        <v>-10.15386792000001</v>
       </c>
       <c r="Q88">
-        <v>112.78327424</v>
+        <v>111.64613208</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4992758235845348</v>
+        <v>0.5341585792448835</v>
       </c>
       <c r="T88">
-        <v>3.161834129954709</v>
+        <v>3.405052139951225</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2723396989241628</v>
+        <v>0.2692093575572183</v>
       </c>
       <c r="W88">
-        <v>0.1068205321979329</v>
+        <v>0.1072800663106004</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9077989964138758</v>
+        <v>0.8973645251907277</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1627742729920572</v>
+        <v>0.1637842729920572</v>
       </c>
       <c r="C89">
-        <v>7.909553568668116</v>
+        <v>-9.816927944467579</v>
       </c>
       <c r="D89">
-        <v>778.0515535686681</v>
+        <v>771.3910720555323</v>
       </c>
       <c r="E89">
-        <v>41.44200000000001</v>
+        <v>52.50799999999992</v>
       </c>
       <c r="F89">
-        <v>962.742</v>
+        <v>973.8079999999999</v>
       </c>
       <c r="G89">
         <v>192.6</v>
@@ -8585,37 +8585,37 @@
         <v>126.825</v>
       </c>
       <c r="M89">
-        <v>141.3305256</v>
+        <v>142.9550144</v>
       </c>
       <c r="N89">
-        <v>-14.50552560000001</v>
+        <v>-16.13001439999998</v>
       </c>
       <c r="O89">
-        <v>-4.351657680000003</v>
+        <v>-4.839004319999994</v>
       </c>
       <c r="P89">
-        <v>-10.15386792000001</v>
+        <v>-11.29101007999999</v>
       </c>
       <c r="Q89">
-        <v>111.64613208</v>
+        <v>110.50898992</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5341585792448835</v>
+        <v>0.5748551275152906</v>
       </c>
       <c r="T89">
-        <v>3.405052139951225</v>
+        <v>3.688806484947161</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2692093575572183</v>
+        <v>0.26615016031225</v>
       </c>
       <c r="W89">
-        <v>0.1072800663106004</v>
+        <v>0.1077291564661617</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8973645251907277</v>
+        <v>0.8871672010408334</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1637842729920572</v>
+        <v>0.1647942729920572</v>
       </c>
       <c r="C90">
-        <v>-9.816927944467579</v>
+        <v>-27.430343741765</v>
       </c>
       <c r="D90">
-        <v>771.3910720555323</v>
+        <v>764.8436562582349</v>
       </c>
       <c r="E90">
-        <v>52.50799999999992</v>
+        <v>63.57399999999996</v>
       </c>
       <c r="F90">
-        <v>973.8079999999999</v>
+        <v>984.8739999999999</v>
       </c>
       <c r="G90">
         <v>192.6</v>
@@ -8667,37 +8667,37 @@
         <v>126.825</v>
       </c>
       <c r="M90">
-        <v>142.9550144</v>
+        <v>144.5795032</v>
       </c>
       <c r="N90">
-        <v>-16.13001439999998</v>
+        <v>-17.7545032</v>
       </c>
       <c r="O90">
-        <v>-4.839004319999994</v>
+        <v>-5.32635096</v>
       </c>
       <c r="P90">
-        <v>-11.29101007999999</v>
+        <v>-12.42815224</v>
       </c>
       <c r="Q90">
-        <v>110.50898992</v>
+        <v>109.37184776</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5748551275152906</v>
+        <v>0.6229510481984989</v>
       </c>
       <c r="T90">
-        <v>3.688806484947161</v>
+        <v>4.024152529033267</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.26615016031225</v>
+        <v>0.2631597090727865</v>
       </c>
       <c r="W90">
-        <v>0.1077291564661617</v>
+        <v>0.108168154708115</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8871672010408334</v>
+        <v>0.8771990302426216</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1647942729920572</v>
+        <v>0.1658042729920572</v>
       </c>
       <c r="C91">
-        <v>-27.430343741765</v>
+        <v>-44.9335486308936</v>
       </c>
       <c r="D91">
-        <v>764.8436562582349</v>
+        <v>758.4064513691063</v>
       </c>
       <c r="E91">
-        <v>63.57399999999996</v>
+        <v>74.63999999999999</v>
       </c>
       <c r="F91">
-        <v>984.8739999999999</v>
+        <v>995.9399999999999</v>
       </c>
       <c r="G91">
         <v>192.6</v>
@@ -8749,37 +8749,37 @@
         <v>126.825</v>
       </c>
       <c r="M91">
-        <v>144.5795032</v>
+        <v>146.203992</v>
       </c>
       <c r="N91">
-        <v>-17.7545032</v>
+        <v>-19.378992</v>
       </c>
       <c r="O91">
-        <v>-5.32635096</v>
+        <v>-5.813697599999998</v>
       </c>
       <c r="P91">
-        <v>-12.42815224</v>
+        <v>-13.5652944</v>
       </c>
       <c r="Q91">
-        <v>109.37184776</v>
+        <v>108.2347056</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6229510481984989</v>
+        <v>0.6806661530183487</v>
       </c>
       <c r="T91">
-        <v>4.024152529033267</v>
+        <v>4.426567781936593</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2631597090727865</v>
+        <v>0.2602357123053111</v>
       </c>
       <c r="W91">
-        <v>0.108168154708115</v>
+        <v>0.1085973974335804</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8771990302426216</v>
+        <v>0.8674523743510369</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1658042729920572</v>
+        <v>0.1668142729920572</v>
       </c>
       <c r="C92">
-        <v>-44.9335486308936</v>
+        <v>-62.32930211322139</v>
       </c>
       <c r="D92">
-        <v>758.4064513691063</v>
+        <v>752.0766978867786</v>
       </c>
       <c r="E92">
-        <v>74.63999999999999</v>
+        <v>85.70600000000002</v>
       </c>
       <c r="F92">
-        <v>995.9399999999999</v>
+        <v>1007.006</v>
       </c>
       <c r="G92">
         <v>192.6</v>
@@ -8831,37 +8831,37 @@
         <v>126.825</v>
       </c>
       <c r="M92">
-        <v>146.203992</v>
+        <v>147.8284808</v>
       </c>
       <c r="N92">
-        <v>-19.378992</v>
+        <v>-21.00348080000002</v>
       </c>
       <c r="O92">
-        <v>-5.813697599999998</v>
+        <v>-6.301044240000006</v>
       </c>
       <c r="P92">
-        <v>-13.5652944</v>
+        <v>-14.70243656000001</v>
       </c>
       <c r="Q92">
-        <v>108.2347056</v>
+        <v>107.09756344</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6806661530183487</v>
+        <v>0.7512068366870543</v>
       </c>
       <c r="T92">
-        <v>4.426567781936593</v>
+        <v>4.918408646596216</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2602357123053111</v>
+        <v>0.2573759792030549</v>
       </c>
       <c r="W92">
-        <v>0.1085973974335804</v>
+        <v>0.1090172062529915</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8674523743510369</v>
+        <v>0.8579199306768496</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1668142729920572</v>
+        <v>0.1678242729920572</v>
       </c>
       <c r="C93">
-        <v>-62.32930211322139</v>
+        <v>-79.62027232808259</v>
       </c>
       <c r="D93">
-        <v>752.0766978867786</v>
+        <v>745.8517276719174</v>
       </c>
       <c r="E93">
-        <v>85.70600000000002</v>
+        <v>96.77200000000005</v>
       </c>
       <c r="F93">
-        <v>1007.006</v>
+        <v>1018.072</v>
       </c>
       <c r="G93">
         <v>192.6</v>
@@ -8913,37 +8913,37 @@
         <v>126.825</v>
       </c>
       <c r="M93">
-        <v>147.8284808</v>
+        <v>149.4529696</v>
       </c>
       <c r="N93">
-        <v>-21.00348080000002</v>
+        <v>-22.62796960000001</v>
       </c>
       <c r="O93">
-        <v>-6.301044240000006</v>
+        <v>-6.788390880000004</v>
       </c>
       <c r="P93">
-        <v>-14.70243656000001</v>
+        <v>-15.83957872000001</v>
       </c>
       <c r="Q93">
-        <v>107.09756344</v>
+        <v>105.96042128</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7512068366870543</v>
+        <v>0.8393826912729363</v>
       </c>
       <c r="T93">
-        <v>4.918408646596216</v>
+        <v>5.533209727420744</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2573759792030549</v>
+        <v>0.2545784142117173</v>
       </c>
       <c r="W93">
-        <v>0.1090172062529915</v>
+        <v>0.1094278887937199</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8579199306768496</v>
+        <v>0.8485947140390577</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1678242729920572</v>
+        <v>0.1688342729920572</v>
       </c>
       <c r="C94">
-        <v>-79.62027232808259</v>
+        <v>-96.80903980277822</v>
       </c>
       <c r="D94">
-        <v>745.8517276719174</v>
+        <v>739.7289601972217</v>
       </c>
       <c r="E94">
-        <v>96.77200000000005</v>
+        <v>107.838</v>
       </c>
       <c r="F94">
-        <v>1018.072</v>
+        <v>1029.138</v>
       </c>
       <c r="G94">
         <v>192.6</v>
@@ -8995,37 +8995,37 @@
         <v>126.825</v>
       </c>
       <c r="M94">
-        <v>149.4529696</v>
+        <v>151.0774584</v>
       </c>
       <c r="N94">
-        <v>-22.62796960000001</v>
+        <v>-24.25245840000001</v>
       </c>
       <c r="O94">
-        <v>-6.788390880000004</v>
+        <v>-7.275737520000003</v>
       </c>
       <c r="P94">
-        <v>-15.83957872000001</v>
+        <v>-16.97672088000001</v>
       </c>
       <c r="Q94">
-        <v>105.96042128</v>
+        <v>104.82327912</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8393826912729363</v>
+        <v>0.95275164716907</v>
       </c>
       <c r="T94">
-        <v>5.533209727420744</v>
+        <v>6.323668259909422</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2545784142117173</v>
+        <v>0.2518410119083656</v>
       </c>
       <c r="W94">
-        <v>0.1094278887937199</v>
+        <v>0.1098297394518519</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8485947140390577</v>
+        <v>0.8394700396945518</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1688342729920572</v>
+        <v>0.1698442729920572</v>
       </c>
       <c r="C95">
-        <v>-96.80903980277822</v>
+        <v>-113.8981010193734</v>
       </c>
       <c r="D95">
-        <v>739.7289601972217</v>
+        <v>733.7058989806266</v>
       </c>
       <c r="E95">
-        <v>107.838</v>
+        <v>118.904</v>
       </c>
       <c r="F95">
-        <v>1029.138</v>
+        <v>1040.204</v>
       </c>
       <c r="G95">
         <v>192.6</v>
@@ -9077,37 +9077,37 @@
         <v>126.825</v>
       </c>
       <c r="M95">
-        <v>151.0774584</v>
+        <v>152.7019472</v>
       </c>
       <c r="N95">
-        <v>-24.25245840000001</v>
+        <v>-25.8769472</v>
       </c>
       <c r="O95">
-        <v>-7.275737520000003</v>
+        <v>-7.763084160000001</v>
       </c>
       <c r="P95">
-        <v>-16.97672088000001</v>
+        <v>-18.11386304</v>
       </c>
       <c r="Q95">
-        <v>104.82327912</v>
+        <v>103.68613696</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.95275164716907</v>
+        <v>1.103910255030582</v>
       </c>
       <c r="T95">
-        <v>6.323668259909422</v>
+        <v>7.377612969894328</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2518410119083656</v>
+        <v>0.2491618522072127</v>
       </c>
       <c r="W95">
-        <v>0.1098297394518519</v>
+        <v>0.1102230400959812</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8394700396945518</v>
+        <v>0.8305395073573757</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1698442729920572</v>
+        <v>0.1708542729920572</v>
       </c>
       <c r="C96">
-        <v>-113.8981010193734</v>
+        <v>-130.8898718086491</v>
       </c>
       <c r="D96">
-        <v>733.7058989806266</v>
+        <v>727.7801281913509</v>
       </c>
       <c r="E96">
-        <v>118.904</v>
+        <v>129.97</v>
       </c>
       <c r="F96">
-        <v>1040.204</v>
+        <v>1051.27</v>
       </c>
       <c r="G96">
         <v>192.6</v>
@@ -9159,37 +9159,37 @@
         <v>126.825</v>
       </c>
       <c r="M96">
-        <v>152.7019472</v>
+        <v>154.326436</v>
       </c>
       <c r="N96">
-        <v>-25.8769472</v>
+        <v>-27.501436</v>
       </c>
       <c r="O96">
-        <v>-7.763084160000001</v>
+        <v>-8.250430799999998</v>
       </c>
       <c r="P96">
-        <v>-18.11386304</v>
+        <v>-19.2510052</v>
       </c>
       <c r="Q96">
-        <v>103.68613696</v>
+        <v>102.5489948</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.103910255030582</v>
+        <v>1.315532306036699</v>
       </c>
       <c r="T96">
-        <v>7.377612969894328</v>
+        <v>8.853135563873197</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2491618522072127</v>
+        <v>0.2465390958681894</v>
       </c>
       <c r="W96">
-        <v>0.1102230400959812</v>
+        <v>0.1106080607265498</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8305395073573757</v>
+        <v>0.8217969862272981</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1708542729920572</v>
+        <v>0.1718642729920572</v>
       </c>
       <c r="C97">
-        <v>-130.8898718086491</v>
+        <v>-147.7866905809082</v>
       </c>
       <c r="D97">
-        <v>727.7801281913509</v>
+        <v>721.9493094190918</v>
       </c>
       <c r="E97">
-        <v>129.97</v>
+        <v>141.0360000000001</v>
       </c>
       <c r="F97">
-        <v>1051.27</v>
+        <v>1062.336</v>
       </c>
       <c r="G97">
         <v>192.6</v>
@@ -9241,37 +9241,37 @@
         <v>126.825</v>
       </c>
       <c r="M97">
-        <v>154.326436</v>
+        <v>155.9509248</v>
       </c>
       <c r="N97">
-        <v>-27.501436</v>
+        <v>-29.12592480000002</v>
       </c>
       <c r="O97">
-        <v>-8.250430799999998</v>
+        <v>-8.737777440000006</v>
       </c>
       <c r="P97">
-        <v>-19.2510052</v>
+        <v>-20.38814736000002</v>
       </c>
       <c r="Q97">
-        <v>102.5489948</v>
+        <v>101.41185264</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.315532306036699</v>
+        <v>1.632965382545875</v>
       </c>
       <c r="T97">
-        <v>8.853135563873197</v>
+        <v>11.0664194548415</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2465390958681894</v>
+        <v>0.2439709802862291</v>
       </c>
       <c r="W97">
-        <v>0.1106080607265498</v>
+        <v>0.1109850600939816</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8217969862272981</v>
+        <v>0.813236600954097</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1718642729920572</v>
+        <v>0.1728742729920572</v>
       </c>
       <c r="C98">
-        <v>-147.7866905809078</v>
+        <v>-164.5908214027061</v>
       </c>
       <c r="D98">
-        <v>721.9493094190919</v>
+        <v>716.2111785972937</v>
       </c>
       <c r="E98">
-        <v>141.0359999999998</v>
+        <v>152.1019999999999</v>
       </c>
       <c r="F98">
-        <v>1062.336</v>
+        <v>1073.402</v>
       </c>
       <c r="G98">
         <v>192.6</v>
@@ -9323,37 +9323,37 @@
         <v>126.825</v>
       </c>
       <c r="M98">
-        <v>155.9509248</v>
+        <v>157.5754136</v>
       </c>
       <c r="N98">
-        <v>-29.12592479999999</v>
+        <v>-30.75041359999999</v>
       </c>
       <c r="O98">
-        <v>-8.737777439999997</v>
+        <v>-9.225124079999995</v>
       </c>
       <c r="P98">
-        <v>-20.38814736</v>
+        <v>-21.52528951999999</v>
       </c>
       <c r="Q98">
-        <v>101.41185264</v>
+        <v>100.27471048</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.63296538254587</v>
+        <v>2.16202051006116</v>
       </c>
       <c r="T98">
-        <v>11.06641945484147</v>
+        <v>14.75522593978863</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2439709802862291</v>
+        <v>0.2414558155410103</v>
       </c>
       <c r="W98">
-        <v>0.1109850600939816</v>
+        <v>0.1113542862785797</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8132366009540971</v>
+        <v>0.8048527184700343</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1728742729920572</v>
+        <v>0.232025987853253</v>
       </c>
       <c r="C99">
-        <v>-164.5908214027061</v>
+        <v>-403.1498791931797</v>
       </c>
       <c r="D99">
-        <v>716.2111785972937</v>
+        <v>488.7181208068202</v>
       </c>
       <c r="E99">
-        <v>152.1019999999999</v>
+        <v>163.1679999999999</v>
       </c>
       <c r="F99">
-        <v>1073.402</v>
+        <v>1084.468</v>
       </c>
       <c r="G99">
         <v>192.6</v>
@@ -9405,45 +9405,45 @@
         <v>126.825</v>
       </c>
       <c r="M99">
-        <v>157.5754136</v>
+        <v>217.7611744</v>
       </c>
       <c r="N99">
-        <v>-30.75041359999999</v>
+        <v>-90.93617439999998</v>
       </c>
       <c r="O99">
-        <v>-9.225124079999995</v>
+        <v>-27.28085231999999</v>
       </c>
       <c r="P99">
-        <v>-21.52528951999999</v>
+        <v>-63.65532207999999</v>
       </c>
       <c r="Q99">
-        <v>100.27471048</v>
+        <v>58.14467792000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.16202051006116</v>
+        <v>3.481216508151534</v>
       </c>
       <c r="T99">
-        <v>14.75522593978863</v>
+        <v>23.95324425505667</v>
       </c>
       <c r="U99">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.2414558155410103</v>
+        <v>0.1747212289097574</v>
       </c>
       <c r="W99">
-        <v>0.1113542862785797</v>
+        <v>0.1657159772349207</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8048527184700343</v>
+        <v>0.582404096365858</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.232025987853253</v>
+        <v>0.2335759878532531</v>
       </c>
       <c r="C100">
-        <v>-403.1498791931797</v>
+        <v>-418.250011011155</v>
       </c>
       <c r="D100">
-        <v>488.7181208068202</v>
+        <v>484.6839889888448</v>
       </c>
       <c r="E100">
-        <v>163.1679999999999</v>
+        <v>174.2339999999999</v>
       </c>
       <c r="F100">
-        <v>1084.468</v>
+        <v>1095.534</v>
       </c>
       <c r="G100">
         <v>192.6</v>
@@ -9487,37 +9487,37 @@
         <v>126.825</v>
       </c>
       <c r="M100">
-        <v>217.7611744</v>
+        <v>219.9832272</v>
       </c>
       <c r="N100">
-        <v>-90.93617439999998</v>
+        <v>-93.15822719999998</v>
       </c>
       <c r="O100">
-        <v>-27.28085231999999</v>
+        <v>-27.94746816</v>
       </c>
       <c r="P100">
-        <v>-63.65532207999999</v>
+        <v>-65.21075903999999</v>
       </c>
       <c r="Q100">
-        <v>58.14467792000001</v>
+        <v>56.58924096000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.481216508151534</v>
+        <v>6.916633016303068</v>
       </c>
       <c r="T100">
-        <v>23.95324425505667</v>
+        <v>47.90648851011335</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1747212289097574</v>
+        <v>0.172956368011679</v>
       </c>
       <c r="W100">
-        <v>0.1657159772349207</v>
+        <v>0.1660703613032549</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.582404096365858</v>
+        <v>0.5765212267055968</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2335759878532531</v>
-      </c>
-      <c r="C101">
-        <v>-418.250011011155</v>
-      </c>
-      <c r="D101">
-        <v>484.6839889888448</v>
-      </c>
-      <c r="E101">
-        <v>174.2339999999999</v>
-      </c>
-      <c r="F101">
-        <v>1095.534</v>
-      </c>
-      <c r="G101">
-        <v>192.6</v>
-      </c>
-      <c r="H101">
-        <v>185.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>248.625</v>
-      </c>
-      <c r="K101">
-        <v>121.8</v>
-      </c>
-      <c r="L101">
-        <v>126.825</v>
-      </c>
-      <c r="M101">
-        <v>219.9832272</v>
-      </c>
-      <c r="N101">
-        <v>-93.15822719999998</v>
-      </c>
-      <c r="O101">
-        <v>-27.94746816</v>
-      </c>
-      <c r="P101">
-        <v>-65.21075903999999</v>
-      </c>
-      <c r="Q101">
-        <v>56.58924096000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.916633016303068</v>
-      </c>
-      <c r="T101">
-        <v>47.90648851011335</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.172956368011679</v>
-      </c>
-      <c r="W101">
-        <v>0.1660703613032549</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5765212267055968</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
